--- a/Chapter05_Campylobacter_plasmids/Appendix/Appendix04_ILMN_metadata.xlsx
+++ b/Chapter05_Campylobacter_plasmids/Appendix/Appendix04_ILMN_metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://masseyuni.sharepoint.com/teams/Students-AlineParolin/Shared Documents/Aline Parolin Calarga PhD Project/Thesis/Chapter 05 Campy plasmids/Writing_Chapter05/Appendix/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1393" documentId="13_ncr:1_{2E4E2978-847A-4ED3-A5A1-B25FE4FE8C11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6203F3AC-B3EA-450B-B289-7A8F5F86E649}"/>
+  <xr:revisionPtr revIDLastSave="1420" documentId="13_ncr:1_{2E4E2978-847A-4ED3-A5A1-B25FE4FE8C11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7865D925-7B30-4E09-9454-D2D3523ED1E2}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{704F0603-2400-41F4-A44C-EE9A72C5778F}"/>
+    <workbookView xWindow="-24120" yWindow="-840" windowWidth="24240" windowHeight="17520" xr2:uid="{704F0603-2400-41F4-A44C-EE9A72C5778F}"/>
   </bookViews>
   <sheets>
     <sheet name="Illumina_contigs_selected" sheetId="9" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1279" uniqueCount="302">
   <si>
     <t>ID</t>
   </si>
@@ -848,9 +848,6 @@
   </si>
   <si>
     <t>Contig_25_53.7129</t>
-  </si>
-  <si>
-    <t>unknown</t>
   </si>
   <si>
     <t>ND</t>
@@ -1014,7 +1011,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1025,11 +1022,12 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3755,12 +3753,14 @@
   <dimension ref="A1:K177"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="4"/>
+    <col min="2" max="2" width="20.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="9.140625" style="4"/>
+    <col min="10" max="10" width="13.42578125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3777,5159 +3777,5159 @@
         <v>87</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="F1" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="F1" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="4">
         <v>1780</v>
       </c>
-      <c r="E2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F2" t="s">
-        <v>85</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="E2" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="4">
         <v>3072</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="4">
         <v>828</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="D3" s="4">
+        <v>9957</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H3" s="4">
+        <v>520</v>
+      </c>
+      <c r="I3" s="4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="D4" s="4">
+        <v>16031</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H4" s="4">
+        <v>520</v>
+      </c>
+      <c r="I4" s="4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="4">
+        <v>892</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H5" s="4">
+        <v>520</v>
+      </c>
+      <c r="I5" s="4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D6" s="4">
+        <v>22845</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H6" s="4">
+        <v>520</v>
+      </c>
+      <c r="I6" s="4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D7" s="4">
+        <v>15833</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H7" s="4">
+        <v>508</v>
+      </c>
+      <c r="I7" s="4">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D8" s="4">
+        <v>16178</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H8" s="4">
+        <v>12749</v>
+      </c>
+      <c r="I8" s="4">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D9" s="4">
+        <v>8627</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H9" s="4">
+        <v>12749</v>
+      </c>
+      <c r="I9" s="4">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D10" s="4">
+        <v>13267</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" s="4">
+        <v>12749</v>
+      </c>
+      <c r="I10" s="4">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D11" s="4">
+        <v>6098</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11" s="4">
+        <v>12749</v>
+      </c>
+      <c r="I11" s="4">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D12" s="4">
+        <v>3046</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H12" s="4">
+        <v>12749</v>
+      </c>
+      <c r="I12" s="4">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1761</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H13" s="4">
+        <v>12749</v>
+      </c>
+      <c r="I13" s="4">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D14" s="4">
+        <v>31327</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H14" s="4">
+        <v>227</v>
+      </c>
+      <c r="I14" s="4">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D15" s="4">
+        <v>4301</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H15" s="4">
+        <v>354</v>
+      </c>
+      <c r="I15" s="4">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D16" s="4">
+        <v>6534</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H16" s="4">
+        <v>354</v>
+      </c>
+      <c r="I16" s="4">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D17" s="4">
+        <v>4407</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H17" s="4">
+        <v>354</v>
+      </c>
+      <c r="I17" s="4">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D18" s="4">
+        <v>43222</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H18" s="4">
+        <v>354</v>
+      </c>
+      <c r="I18" s="4">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D19" s="4">
+        <v>1386</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H19" s="4">
+        <v>354</v>
+      </c>
+      <c r="I19" s="4">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="4">
+        <v>7528</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H20" s="4">
+        <v>677</v>
+      </c>
+      <c r="I20" s="4">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="D21" s="4">
+        <v>12620</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H21" s="4">
+        <v>677</v>
+      </c>
+      <c r="I21" s="4">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="D22" s="4">
+        <v>8948</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H22" s="4">
+        <v>677</v>
+      </c>
+      <c r="I22" s="4">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="D23" s="4">
+        <v>12633</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H23" s="4">
+        <v>48</v>
+      </c>
+      <c r="I23" s="4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="D3">
-        <v>9957</v>
-      </c>
-      <c r="E3" t="s">
-        <v>85</v>
-      </c>
-      <c r="F3" t="s">
-        <v>85</v>
-      </c>
-      <c r="G3" t="s">
-        <v>67</v>
-      </c>
-      <c r="H3">
-        <v>520</v>
-      </c>
-      <c r="I3">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C4" t="s">
-        <v>296</v>
-      </c>
-      <c r="D4">
-        <v>16031</v>
-      </c>
-      <c r="E4" t="s">
-        <v>85</v>
-      </c>
-      <c r="F4" t="s">
-        <v>85</v>
-      </c>
-      <c r="G4" t="s">
-        <v>67</v>
-      </c>
-      <c r="H4">
-        <v>520</v>
-      </c>
-      <c r="I4">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5">
-        <v>892</v>
-      </c>
-      <c r="E5" t="s">
-        <v>85</v>
-      </c>
-      <c r="F5" t="s">
-        <v>85</v>
-      </c>
-      <c r="G5" t="s">
-        <v>67</v>
-      </c>
-      <c r="H5">
-        <v>520</v>
-      </c>
-      <c r="I5">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D6">
-        <v>22845</v>
-      </c>
-      <c r="E6" t="s">
-        <v>85</v>
-      </c>
-      <c r="F6" t="s">
-        <v>85</v>
-      </c>
-      <c r="G6" t="s">
-        <v>67</v>
-      </c>
-      <c r="H6">
-        <v>520</v>
-      </c>
-      <c r="I6">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>66</v>
-      </c>
-      <c r="B7" t="s">
-        <v>216</v>
-      </c>
-      <c r="C7" t="s">
-        <v>215</v>
-      </c>
-      <c r="D7">
-        <v>15833</v>
-      </c>
-      <c r="E7" t="s">
-        <v>85</v>
-      </c>
-      <c r="F7" t="s">
-        <v>85</v>
-      </c>
-      <c r="G7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H7">
-        <v>508</v>
-      </c>
-      <c r="I7">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" t="s">
-        <v>217</v>
-      </c>
-      <c r="C8" t="s">
-        <v>215</v>
-      </c>
-      <c r="D8">
-        <v>16178</v>
-      </c>
-      <c r="E8" t="s">
-        <v>85</v>
-      </c>
-      <c r="F8" t="s">
-        <v>85</v>
-      </c>
-      <c r="G8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H8">
-        <v>12749</v>
-      </c>
-      <c r="I8" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>68</v>
-      </c>
-      <c r="B9" t="s">
-        <v>218</v>
-      </c>
-      <c r="C9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D9">
-        <v>8627</v>
-      </c>
-      <c r="E9" t="s">
-        <v>85</v>
-      </c>
-      <c r="F9" t="s">
-        <v>85</v>
-      </c>
-      <c r="G9" t="s">
-        <v>67</v>
-      </c>
-      <c r="H9">
-        <v>12749</v>
-      </c>
-      <c r="I9" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>68</v>
-      </c>
-      <c r="B10" t="s">
-        <v>219</v>
-      </c>
-      <c r="C10" t="s">
-        <v>215</v>
-      </c>
-      <c r="D10">
-        <v>13267</v>
-      </c>
-      <c r="E10" t="s">
-        <v>85</v>
-      </c>
-      <c r="F10" t="s">
-        <v>85</v>
-      </c>
-      <c r="G10" t="s">
-        <v>67</v>
-      </c>
-      <c r="H10">
-        <v>12749</v>
-      </c>
-      <c r="I10" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>68</v>
-      </c>
-      <c r="B11" t="s">
-        <v>220</v>
-      </c>
-      <c r="C11" t="s">
-        <v>215</v>
-      </c>
-      <c r="D11">
-        <v>6098</v>
-      </c>
-      <c r="E11" t="s">
-        <v>85</v>
-      </c>
-      <c r="F11" t="s">
-        <v>85</v>
-      </c>
-      <c r="G11" t="s">
-        <v>67</v>
-      </c>
-      <c r="H11">
-        <v>12749</v>
-      </c>
-      <c r="I11" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>68</v>
-      </c>
-      <c r="B12" t="s">
-        <v>221</v>
-      </c>
-      <c r="C12" t="s">
-        <v>215</v>
-      </c>
-      <c r="D12">
-        <v>3046</v>
-      </c>
-      <c r="E12" t="s">
-        <v>85</v>
-      </c>
-      <c r="F12" t="s">
-        <v>85</v>
-      </c>
-      <c r="G12" t="s">
-        <v>67</v>
-      </c>
-      <c r="H12">
-        <v>12749</v>
-      </c>
-      <c r="I12" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>68</v>
-      </c>
-      <c r="B13" t="s">
-        <v>222</v>
-      </c>
-      <c r="C13" t="s">
-        <v>215</v>
-      </c>
-      <c r="D13">
-        <v>1761</v>
-      </c>
-      <c r="E13" t="s">
-        <v>85</v>
-      </c>
-      <c r="F13" t="s">
-        <v>85</v>
-      </c>
-      <c r="G13" t="s">
-        <v>67</v>
-      </c>
-      <c r="H13">
-        <v>12749</v>
-      </c>
-      <c r="I13" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>69</v>
-      </c>
-      <c r="B14" t="s">
-        <v>223</v>
-      </c>
-      <c r="C14" t="s">
-        <v>215</v>
-      </c>
-      <c r="D14">
-        <v>31327</v>
-      </c>
-      <c r="E14" t="s">
-        <v>85</v>
-      </c>
-      <c r="F14" t="s">
-        <v>85</v>
-      </c>
-      <c r="G14" t="s">
-        <v>67</v>
-      </c>
-      <c r="H14">
-        <v>227</v>
-      </c>
-      <c r="I14">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>70</v>
-      </c>
-      <c r="B15" t="s">
-        <v>224</v>
-      </c>
-      <c r="C15" t="s">
-        <v>215</v>
-      </c>
-      <c r="D15">
-        <v>4301</v>
-      </c>
-      <c r="E15" t="s">
-        <v>85</v>
-      </c>
-      <c r="F15" t="s">
-        <v>85</v>
-      </c>
-      <c r="G15" t="s">
-        <v>67</v>
-      </c>
-      <c r="H15">
-        <v>354</v>
-      </c>
-      <c r="I15">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16" t="s">
-        <v>225</v>
-      </c>
-      <c r="C16" t="s">
-        <v>215</v>
-      </c>
-      <c r="D16">
-        <v>6534</v>
-      </c>
-      <c r="E16" t="s">
-        <v>85</v>
-      </c>
-      <c r="F16" t="s">
-        <v>85</v>
-      </c>
-      <c r="G16" t="s">
-        <v>67</v>
-      </c>
-      <c r="H16">
-        <v>354</v>
-      </c>
-      <c r="I16">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>70</v>
-      </c>
-      <c r="B17" t="s">
-        <v>226</v>
-      </c>
-      <c r="C17" t="s">
-        <v>215</v>
-      </c>
-      <c r="D17">
-        <v>4407</v>
-      </c>
-      <c r="E17" t="s">
-        <v>85</v>
-      </c>
-      <c r="F17" t="s">
-        <v>85</v>
-      </c>
-      <c r="G17" t="s">
-        <v>67</v>
-      </c>
-      <c r="H17">
-        <v>354</v>
-      </c>
-      <c r="I17">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>70</v>
-      </c>
-      <c r="B18" t="s">
-        <v>227</v>
-      </c>
-      <c r="C18" t="s">
-        <v>215</v>
-      </c>
-      <c r="D18">
-        <v>43222</v>
-      </c>
-      <c r="E18" t="s">
-        <v>85</v>
-      </c>
-      <c r="F18" t="s">
-        <v>85</v>
-      </c>
-      <c r="G18" t="s">
-        <v>67</v>
-      </c>
-      <c r="H18">
-        <v>354</v>
-      </c>
-      <c r="I18">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>70</v>
-      </c>
-      <c r="B19" t="s">
-        <v>228</v>
-      </c>
-      <c r="C19" t="s">
-        <v>215</v>
-      </c>
-      <c r="D19">
-        <v>1386</v>
-      </c>
-      <c r="E19" t="s">
-        <v>85</v>
-      </c>
-      <c r="F19" t="s">
-        <v>85</v>
-      </c>
-      <c r="G19" t="s">
-        <v>67</v>
-      </c>
-      <c r="H19">
-        <v>354</v>
-      </c>
-      <c r="I19">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" t="s">
-        <v>93</v>
-      </c>
-      <c r="C20" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20">
-        <v>7528</v>
-      </c>
-      <c r="E20" t="s">
-        <v>85</v>
-      </c>
-      <c r="F20" t="s">
-        <v>85</v>
-      </c>
-      <c r="G20" t="s">
-        <v>67</v>
-      </c>
-      <c r="H20">
-        <v>677</v>
-      </c>
-      <c r="I20">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" t="s">
-        <v>94</v>
-      </c>
-      <c r="C21" t="s">
-        <v>297</v>
-      </c>
-      <c r="D21">
-        <v>12620</v>
-      </c>
-      <c r="E21" t="s">
-        <v>85</v>
-      </c>
-      <c r="F21" t="s">
-        <v>85</v>
-      </c>
-      <c r="G21" t="s">
-        <v>67</v>
-      </c>
-      <c r="H21">
-        <v>677</v>
-      </c>
-      <c r="I21">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" t="s">
-        <v>95</v>
-      </c>
-      <c r="C22" t="s">
-        <v>284</v>
-      </c>
-      <c r="D22">
-        <v>8948</v>
-      </c>
-      <c r="E22" t="s">
-        <v>85</v>
-      </c>
-      <c r="F22" t="s">
-        <v>85</v>
-      </c>
-      <c r="G22" t="s">
-        <v>67</v>
-      </c>
-      <c r="H22">
-        <v>677</v>
-      </c>
-      <c r="I22">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>9</v>
-      </c>
-      <c r="B23" t="s">
-        <v>96</v>
-      </c>
-      <c r="C23" t="s">
-        <v>292</v>
-      </c>
-      <c r="D23">
-        <v>12633</v>
-      </c>
-      <c r="E23" t="s">
-        <v>85</v>
-      </c>
-      <c r="F23" t="s">
-        <v>85</v>
-      </c>
-      <c r="G23" t="s">
-        <v>67</v>
-      </c>
-      <c r="H23">
+      <c r="D24" s="4">
+        <v>30787</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H24" s="4">
         <v>48</v>
       </c>
-      <c r="I23">
+      <c r="I24" s="4">
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>9</v>
-      </c>
-      <c r="B24" t="s">
-        <v>97</v>
-      </c>
-      <c r="C24" t="s">
-        <v>285</v>
-      </c>
-      <c r="D24">
-        <v>30787</v>
-      </c>
-      <c r="E24" t="s">
-        <v>85</v>
-      </c>
-      <c r="F24" t="s">
-        <v>85</v>
-      </c>
-      <c r="G24" t="s">
-        <v>67</v>
-      </c>
-      <c r="H24">
-        <v>48</v>
-      </c>
-      <c r="I24">
-        <v>48</v>
-      </c>
-    </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="A25" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="C25" t="s">
-        <v>281</v>
-      </c>
-      <c r="D25">
+      <c r="C25" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="D25" s="4">
         <v>4495</v>
       </c>
-      <c r="E25" t="s">
-        <v>279</v>
-      </c>
-      <c r="F25" t="str">
+      <c r="E25" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="F25" s="4" t="str">
         <f>VLOOKUP(B25,[1]colour_range_groups!$B$2:$F$140,5,FALSE)</f>
         <v>C02</v>
       </c>
-      <c r="G25" t="s">
-        <v>67</v>
-      </c>
-      <c r="H25">
+      <c r="G25" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H25" s="4">
         <v>704</v>
       </c>
-      <c r="I25" t="s">
-        <v>269</v>
+      <c r="I25" s="4" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="A26" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="4">
         <v>38712</v>
       </c>
-      <c r="E26" t="s">
-        <v>85</v>
-      </c>
-      <c r="F26" t="s">
-        <v>85</v>
-      </c>
-      <c r="G26" t="s">
-        <v>67</v>
-      </c>
-      <c r="H26">
+      <c r="E26" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H26" s="4">
         <v>1030</v>
       </c>
-      <c r="I26" t="s">
-        <v>269</v>
+      <c r="I26" s="4" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="A27" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="4">
         <v>29801</v>
       </c>
-      <c r="E27" t="s">
-        <v>85</v>
-      </c>
-      <c r="F27" t="s">
-        <v>85</v>
-      </c>
-      <c r="G27" t="s">
-        <v>67</v>
-      </c>
-      <c r="H27">
+      <c r="E27" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H27" s="4">
         <v>61</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="4">
         <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="A28" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="4">
         <v>20835</v>
       </c>
-      <c r="E28" t="s">
-        <v>85</v>
-      </c>
-      <c r="F28" t="s">
-        <v>85</v>
-      </c>
-      <c r="G28" t="s">
-        <v>67</v>
-      </c>
-      <c r="H28">
+      <c r="E28" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H28" s="4">
         <v>137</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="4">
         <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="A29" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="4">
         <v>17513</v>
       </c>
-      <c r="E29" t="s">
-        <v>85</v>
-      </c>
-      <c r="F29" t="s">
-        <v>85</v>
-      </c>
-      <c r="G29" t="s">
-        <v>67</v>
-      </c>
-      <c r="H29">
+      <c r="E29" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H29" s="4">
         <v>257</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="4">
         <v>257</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="A30" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="4">
         <v>6402</v>
       </c>
-      <c r="E30" t="s">
-        <v>85</v>
-      </c>
-      <c r="F30" t="s">
-        <v>85</v>
-      </c>
-      <c r="G30" t="s">
-        <v>67</v>
-      </c>
-      <c r="H30">
+      <c r="E30" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H30" s="4">
         <v>257</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="4">
         <v>257</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="A31" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="4">
         <v>24881</v>
       </c>
-      <c r="E31" t="s">
-        <v>85</v>
-      </c>
-      <c r="F31" t="s">
-        <v>85</v>
-      </c>
-      <c r="G31" t="s">
-        <v>67</v>
-      </c>
-      <c r="H31">
+      <c r="E31" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H31" s="4">
         <v>474</v>
       </c>
-      <c r="I31">
+      <c r="I31" s="4">
         <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="A32" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="4">
         <v>21971</v>
       </c>
-      <c r="E32" t="s">
-        <v>85</v>
-      </c>
-      <c r="F32" t="s">
-        <v>85</v>
-      </c>
-      <c r="G32" t="s">
-        <v>67</v>
-      </c>
-      <c r="H32">
+      <c r="E32" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H32" s="4">
         <v>474</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="4">
         <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="A33" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="4">
         <v>1470</v>
       </c>
-      <c r="E33" t="s">
-        <v>85</v>
-      </c>
-      <c r="F33" t="s">
-        <v>85</v>
-      </c>
-      <c r="G33" t="s">
-        <v>67</v>
-      </c>
-      <c r="H33">
+      <c r="E33" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H33" s="4">
         <v>474</v>
       </c>
-      <c r="I33">
+      <c r="I33" s="4">
         <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="A34" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="4">
         <v>2938</v>
       </c>
-      <c r="E34" t="s">
-        <v>85</v>
-      </c>
-      <c r="F34" t="s">
-        <v>85</v>
-      </c>
-      <c r="G34" t="s">
-        <v>67</v>
-      </c>
-      <c r="H34">
+      <c r="E34" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H34" s="4">
         <v>474</v>
       </c>
-      <c r="I34">
+      <c r="I34" s="4">
         <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="A35" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="4">
         <v>4093</v>
       </c>
-      <c r="E35" t="s">
-        <v>85</v>
-      </c>
-      <c r="F35" t="s">
-        <v>85</v>
-      </c>
-      <c r="G35" t="s">
-        <v>67</v>
-      </c>
-      <c r="H35">
+      <c r="E35" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H35" s="4">
         <v>535</v>
       </c>
-      <c r="I35">
+      <c r="I35" s="4">
         <v>460</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="A36" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="4">
         <v>16562</v>
       </c>
-      <c r="E36" t="s">
-        <v>85</v>
-      </c>
-      <c r="F36" t="s">
-        <v>85</v>
-      </c>
-      <c r="G36" t="s">
-        <v>67</v>
-      </c>
-      <c r="H36">
+      <c r="E36" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H36" s="4">
         <v>3538</v>
       </c>
-      <c r="I36" t="s">
-        <v>269</v>
+      <c r="I36" s="4" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="A37" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="4">
         <v>18306</v>
       </c>
-      <c r="E37" t="s">
-        <v>85</v>
-      </c>
-      <c r="F37" t="s">
-        <v>85</v>
-      </c>
-      <c r="G37" t="s">
-        <v>67</v>
-      </c>
-      <c r="H37">
+      <c r="E37" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H37" s="4">
         <v>3538</v>
       </c>
-      <c r="I37" t="s">
-        <v>269</v>
+      <c r="I37" s="4" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="A38" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="4">
         <v>4808</v>
       </c>
-      <c r="E38" t="s">
-        <v>85</v>
-      </c>
-      <c r="F38" t="s">
-        <v>85</v>
-      </c>
-      <c r="G38" t="s">
-        <v>67</v>
-      </c>
-      <c r="H38">
+      <c r="E38" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H38" s="4">
         <v>3538</v>
       </c>
-      <c r="I38" t="s">
-        <v>269</v>
+      <c r="I38" s="4" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="A39" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="4">
         <v>6401</v>
       </c>
-      <c r="E39" t="s">
-        <v>85</v>
-      </c>
-      <c r="F39" t="s">
-        <v>85</v>
-      </c>
-      <c r="G39" t="s">
-        <v>67</v>
-      </c>
-      <c r="H39">
+      <c r="E39" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H39" s="4">
         <v>3538</v>
       </c>
-      <c r="I39" t="s">
-        <v>269</v>
+      <c r="I39" s="4" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="A40" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="4">
         <v>25468</v>
       </c>
-      <c r="E40" t="s">
-        <v>85</v>
-      </c>
-      <c r="F40" t="s">
-        <v>85</v>
-      </c>
-      <c r="G40" t="s">
-        <v>67</v>
-      </c>
-      <c r="H40">
+      <c r="E40" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H40" s="4">
         <v>42</v>
       </c>
-      <c r="I40">
+      <c r="I40" s="4">
         <v>42</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="A41" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C41" t="s">
-        <v>284</v>
-      </c>
-      <c r="D41">
+      <c r="C41" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="D41" s="4">
         <v>7021</v>
       </c>
-      <c r="E41" t="s">
-        <v>85</v>
-      </c>
-      <c r="F41" t="s">
-        <v>85</v>
-      </c>
-      <c r="G41" t="s">
-        <v>67</v>
-      </c>
-      <c r="H41">
+      <c r="E41" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H41" s="4">
         <v>42</v>
       </c>
-      <c r="I41">
+      <c r="I41" s="4">
         <v>42</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="A42" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="4">
         <v>29326</v>
       </c>
-      <c r="E42" t="s">
-        <v>85</v>
-      </c>
-      <c r="F42" t="s">
-        <v>85</v>
-      </c>
-      <c r="G42" t="s">
-        <v>67</v>
-      </c>
-      <c r="H42">
+      <c r="E42" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H42" s="4">
         <v>42</v>
       </c>
-      <c r="I42">
+      <c r="I42" s="4">
         <v>42</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="A43" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="4">
         <v>16839</v>
       </c>
-      <c r="E43" t="s">
-        <v>85</v>
-      </c>
-      <c r="F43" t="s">
-        <v>85</v>
-      </c>
-      <c r="G43" t="s">
-        <v>67</v>
-      </c>
-      <c r="H43">
+      <c r="E43" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H43" s="4">
         <v>403</v>
       </c>
-      <c r="I43">
+      <c r="I43" s="4">
         <v>403</v>
       </c>
-      <c r="J43" t="s">
+      <c r="J43" s="4" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D44" s="4">
+        <v>11851</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H44" s="4">
+        <v>403</v>
+      </c>
+      <c r="I44" s="4">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D45" s="4">
+        <v>6513</v>
+      </c>
+      <c r="E45" s="4" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>74</v>
-      </c>
-      <c r="B44" t="s">
-        <v>240</v>
-      </c>
-      <c r="C44" t="s">
-        <v>215</v>
-      </c>
-      <c r="D44">
-        <v>11851</v>
-      </c>
-      <c r="E44" t="s">
-        <v>85</v>
-      </c>
-      <c r="F44" t="s">
-        <v>85</v>
-      </c>
-      <c r="G44" t="s">
-        <v>67</v>
-      </c>
-      <c r="H44">
-        <v>403</v>
-      </c>
-      <c r="I44">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>74</v>
-      </c>
-      <c r="B45" t="s">
-        <v>241</v>
-      </c>
-      <c r="C45" t="s">
-        <v>215</v>
-      </c>
-      <c r="D45">
-        <v>6513</v>
-      </c>
-      <c r="E45" t="s">
-        <v>279</v>
-      </c>
-      <c r="F45" t="str">
+      <c r="F45" s="4" t="str">
         <f>VLOOKUP(B45,[1]colour_range_groups!$B$2:$F$140,5,FALSE)</f>
         <v>C06</v>
       </c>
-      <c r="G45" t="s">
-        <v>67</v>
-      </c>
-      <c r="H45">
+      <c r="G45" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H45" s="4">
         <v>403</v>
       </c>
-      <c r="I45">
+      <c r="I45" s="4">
         <v>403</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+      <c r="A46" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="4">
         <v>4278</v>
       </c>
-      <c r="E46" t="s">
-        <v>85</v>
-      </c>
-      <c r="F46" t="s">
-        <v>85</v>
-      </c>
-      <c r="G46" t="s">
-        <v>67</v>
-      </c>
-      <c r="H46">
+      <c r="E46" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H46" s="4">
         <v>403</v>
       </c>
-      <c r="I46">
+      <c r="I46" s="4">
         <v>403</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+      <c r="A47" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="4">
         <v>5373</v>
       </c>
-      <c r="E47" t="s">
-        <v>85</v>
-      </c>
-      <c r="F47" t="s">
-        <v>85</v>
-      </c>
-      <c r="G47" t="s">
-        <v>67</v>
-      </c>
-      <c r="H47">
+      <c r="E47" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H47" s="4">
         <v>403</v>
       </c>
-      <c r="I47">
+      <c r="I47" s="4">
         <v>403</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="A48" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="4">
         <v>1831</v>
       </c>
-      <c r="E48" t="s">
-        <v>85</v>
-      </c>
-      <c r="F48" t="s">
-        <v>85</v>
-      </c>
-      <c r="G48" t="s">
-        <v>67</v>
-      </c>
-      <c r="H48">
+      <c r="E48" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H48" s="4">
         <v>403</v>
       </c>
-      <c r="I48">
+      <c r="I48" s="4">
         <v>403</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+      <c r="A49" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="4">
         <v>10647</v>
       </c>
-      <c r="E49" t="s">
-        <v>85</v>
-      </c>
-      <c r="F49" t="s">
-        <v>85</v>
-      </c>
-      <c r="G49" t="s">
-        <v>67</v>
-      </c>
-      <c r="H49">
+      <c r="E49" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H49" s="4">
         <v>403</v>
       </c>
-      <c r="I49">
+      <c r="I49" s="4">
         <v>403</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="A50" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D50">
+      <c r="D50" s="4">
         <v>1846</v>
       </c>
-      <c r="E50" t="s">
-        <v>85</v>
-      </c>
-      <c r="F50" t="s">
-        <v>85</v>
-      </c>
-      <c r="G50" t="s">
-        <v>67</v>
-      </c>
-      <c r="H50">
+      <c r="E50" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H50" s="4">
         <v>403</v>
       </c>
-      <c r="I50">
+      <c r="I50" s="4">
         <v>403</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+      <c r="A51" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D51">
+      <c r="D51" s="4">
         <v>3878</v>
       </c>
-      <c r="E51" t="s">
-        <v>85</v>
-      </c>
-      <c r="F51" t="s">
-        <v>85</v>
-      </c>
-      <c r="G51" t="s">
-        <v>67</v>
-      </c>
-      <c r="H51">
+      <c r="E51" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H51" s="4">
         <v>403</v>
       </c>
-      <c r="I51">
+      <c r="I51" s="4">
         <v>403</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+      <c r="A52" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="4">
         <v>4587</v>
       </c>
-      <c r="E52" t="s">
-        <v>85</v>
-      </c>
-      <c r="F52" t="s">
-        <v>85</v>
-      </c>
-      <c r="G52" t="s">
-        <v>67</v>
-      </c>
-      <c r="H52">
+      <c r="E52" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H52" s="4">
         <v>403</v>
       </c>
-      <c r="I52">
+      <c r="I52" s="4">
         <v>403</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+      <c r="A53" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="4">
         <v>2423</v>
       </c>
-      <c r="E53" t="s">
-        <v>85</v>
-      </c>
-      <c r="F53" t="s">
-        <v>85</v>
-      </c>
-      <c r="G53" t="s">
-        <v>67</v>
-      </c>
-      <c r="H53">
+      <c r="E53" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H53" s="4">
         <v>403</v>
       </c>
-      <c r="I53">
+      <c r="I53" s="4">
         <v>403</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+      <c r="A54" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="4">
         <v>1661</v>
       </c>
-      <c r="E54" t="s">
-        <v>85</v>
-      </c>
-      <c r="F54" t="s">
-        <v>85</v>
-      </c>
-      <c r="G54" t="s">
-        <v>67</v>
-      </c>
-      <c r="H54">
+      <c r="E54" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H54" s="4">
         <v>403</v>
       </c>
-      <c r="I54">
+      <c r="I54" s="4">
         <v>403</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+      <c r="A55" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="4">
         <v>1270</v>
       </c>
-      <c r="E55" t="s">
-        <v>85</v>
-      </c>
-      <c r="F55" t="s">
-        <v>85</v>
-      </c>
-      <c r="G55" t="s">
-        <v>67</v>
-      </c>
-      <c r="H55">
+      <c r="E55" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H55" s="4">
         <v>403</v>
       </c>
-      <c r="I55">
+      <c r="I55" s="4">
         <v>403</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+      <c r="A56" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="4">
         <v>1236</v>
       </c>
-      <c r="E56" t="s">
-        <v>85</v>
-      </c>
-      <c r="F56" t="s">
-        <v>85</v>
-      </c>
-      <c r="G56" t="s">
-        <v>67</v>
-      </c>
-      <c r="H56">
+      <c r="E56" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H56" s="4">
         <v>403</v>
       </c>
-      <c r="I56">
+      <c r="I56" s="4">
         <v>403</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+      <c r="A57" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="4">
         <v>16429</v>
       </c>
-      <c r="E57" t="s">
-        <v>85</v>
-      </c>
-      <c r="F57" t="s">
-        <v>85</v>
-      </c>
-      <c r="G57" t="s">
-        <v>67</v>
-      </c>
-      <c r="H57">
+      <c r="E57" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H57" s="4">
         <v>2026</v>
       </c>
-      <c r="I57">
+      <c r="I57" s="4">
         <v>403</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+      <c r="A58" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="4">
         <v>11229</v>
       </c>
-      <c r="E58" t="s">
-        <v>85</v>
-      </c>
-      <c r="F58" t="s">
-        <v>85</v>
-      </c>
-      <c r="G58" t="s">
-        <v>67</v>
-      </c>
-      <c r="H58">
+      <c r="E58" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H58" s="4">
         <v>2026</v>
       </c>
-      <c r="I58">
+      <c r="I58" s="4">
         <v>403</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+      <c r="A59" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="4">
         <v>1852</v>
       </c>
-      <c r="E59" t="s">
-        <v>85</v>
-      </c>
-      <c r="F59" t="s">
-        <v>85</v>
-      </c>
-      <c r="G59" t="s">
-        <v>67</v>
-      </c>
-      <c r="H59">
+      <c r="E59" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H59" s="4">
         <v>2026</v>
       </c>
-      <c r="I59">
+      <c r="I59" s="4">
         <v>403</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+      <c r="A60" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D60">
+      <c r="D60" s="4">
         <v>2484</v>
       </c>
-      <c r="E60" t="s">
-        <v>85</v>
-      </c>
-      <c r="F60" t="s">
-        <v>85</v>
-      </c>
-      <c r="G60" t="s">
-        <v>67</v>
-      </c>
-      <c r="H60">
+      <c r="E60" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H60" s="4">
         <v>2026</v>
       </c>
-      <c r="I60">
+      <c r="I60" s="4">
         <v>403</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+      <c r="A61" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="4">
         <v>2315</v>
       </c>
-      <c r="E61" t="s">
-        <v>85</v>
-      </c>
-      <c r="F61" t="s">
-        <v>85</v>
-      </c>
-      <c r="G61" t="s">
-        <v>67</v>
-      </c>
-      <c r="H61">
+      <c r="E61" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H61" s="4">
         <v>2026</v>
       </c>
-      <c r="I61">
+      <c r="I61" s="4">
         <v>403</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+      <c r="A62" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="4">
         <v>10041</v>
       </c>
-      <c r="E62" t="s">
-        <v>85</v>
-      </c>
-      <c r="F62" t="s">
-        <v>85</v>
-      </c>
-      <c r="G62" t="s">
-        <v>67</v>
-      </c>
-      <c r="H62">
+      <c r="E62" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H62" s="4">
         <v>2026</v>
       </c>
-      <c r="I62">
+      <c r="I62" s="4">
         <v>403</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+      <c r="A63" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="4">
         <v>1718</v>
       </c>
-      <c r="E63" t="s">
-        <v>85</v>
-      </c>
-      <c r="F63" t="s">
-        <v>85</v>
-      </c>
-      <c r="G63" t="s">
-        <v>67</v>
-      </c>
-      <c r="H63">
+      <c r="E63" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H63" s="4">
         <v>2026</v>
       </c>
-      <c r="I63">
+      <c r="I63" s="4">
         <v>403</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+      <c r="A64" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="4">
         <v>1345</v>
       </c>
-      <c r="E64" t="s">
-        <v>85</v>
-      </c>
-      <c r="F64" t="s">
-        <v>85</v>
-      </c>
-      <c r="G64" t="s">
-        <v>67</v>
-      </c>
-      <c r="H64">
+      <c r="E64" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H64" s="4">
         <v>2026</v>
       </c>
-      <c r="I64">
+      <c r="I64" s="4">
         <v>403</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+      <c r="A65" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D65">
+      <c r="D65" s="4">
         <v>1236</v>
       </c>
-      <c r="E65" t="s">
-        <v>85</v>
-      </c>
-      <c r="F65" t="s">
-        <v>85</v>
-      </c>
-      <c r="G65" t="s">
-        <v>67</v>
-      </c>
-      <c r="H65">
+      <c r="E65" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H65" s="4">
         <v>2026</v>
       </c>
-      <c r="I65">
+      <c r="I65" s="4">
         <v>403</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+      <c r="A66" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C66" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="D66" s="4">
+        <v>9868</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H66" s="4">
+        <v>3610</v>
+      </c>
+      <c r="I66" s="4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C67" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="D66">
-        <v>9868</v>
-      </c>
-      <c r="E66" t="s">
-        <v>85</v>
-      </c>
-      <c r="F66" t="s">
-        <v>85</v>
-      </c>
-      <c r="G66" t="s">
-        <v>67</v>
-      </c>
-      <c r="H66">
+      <c r="D67" s="4">
+        <v>8803</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H67" s="4">
         <v>3610</v>
       </c>
-      <c r="I66">
+      <c r="I67" s="4">
         <v>21</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B67" t="s">
-        <v>107</v>
-      </c>
-      <c r="C67" t="s">
-        <v>299</v>
-      </c>
-      <c r="D67">
-        <v>8803</v>
-      </c>
-      <c r="E67" t="s">
-        <v>85</v>
-      </c>
-      <c r="F67" t="s">
-        <v>85</v>
-      </c>
-      <c r="G67" t="s">
-        <v>67</v>
-      </c>
-      <c r="H67">
+      <c r="B68" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D68" s="4">
+        <v>46193</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H68" s="4">
         <v>3610</v>
       </c>
-      <c r="I67">
+      <c r="I68" s="4">
         <v>21</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B68" t="s">
-        <v>108</v>
-      </c>
-      <c r="C68" t="s">
-        <v>13</v>
-      </c>
-      <c r="D68">
-        <v>46193</v>
-      </c>
-      <c r="E68" t="s">
-        <v>85</v>
-      </c>
-      <c r="F68" t="s">
-        <v>85</v>
-      </c>
-      <c r="G68" t="s">
-        <v>67</v>
-      </c>
-      <c r="H68">
+      <c r="B69" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="D69" s="4">
+        <v>9390</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H69" s="4">
         <v>3610</v>
       </c>
-      <c r="I68">
+      <c r="I69" s="4">
         <v>21</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>19</v>
-      </c>
-      <c r="B69" t="s">
-        <v>109</v>
-      </c>
-      <c r="C69" t="s">
-        <v>284</v>
-      </c>
-      <c r="D69">
-        <v>9390</v>
-      </c>
-      <c r="E69" t="s">
-        <v>85</v>
-      </c>
-      <c r="F69" t="s">
-        <v>85</v>
-      </c>
-      <c r="G69" t="s">
-        <v>67</v>
-      </c>
-      <c r="H69">
-        <v>3610</v>
-      </c>
-      <c r="I69">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D70" s="4">
+        <v>8314</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H70" s="4">
+        <v>520</v>
+      </c>
+      <c r="I70" s="4">
         <v>21</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B70" t="s">
-        <v>110</v>
-      </c>
-      <c r="C70" t="s">
+      <c r="B71" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D71" s="4">
+        <v>2844</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H71" s="4">
+        <v>520</v>
+      </c>
+      <c r="I71" s="4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="D72" s="4">
+        <v>17076</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H72" s="4">
+        <v>520</v>
+      </c>
+      <c r="I72" s="4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C73" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="D70">
-        <v>8314</v>
-      </c>
-      <c r="E70" t="s">
-        <v>85</v>
-      </c>
-      <c r="F70" t="s">
-        <v>85</v>
-      </c>
-      <c r="G70" t="s">
-        <v>67</v>
-      </c>
-      <c r="H70">
+      <c r="D73" s="4">
+        <v>32186</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H73" s="4">
         <v>520</v>
       </c>
-      <c r="I70">
+      <c r="I73" s="4">
         <v>21</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>20</v>
-      </c>
-      <c r="B71" t="s">
-        <v>111</v>
-      </c>
-      <c r="C71" t="s">
-        <v>17</v>
-      </c>
-      <c r="D71">
-        <v>2844</v>
-      </c>
-      <c r="E71" t="s">
-        <v>85</v>
-      </c>
-      <c r="F71" t="s">
-        <v>85</v>
-      </c>
-      <c r="G71" t="s">
-        <v>67</v>
-      </c>
-      <c r="H71">
-        <v>520</v>
-      </c>
-      <c r="I71">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D74" s="4">
+        <v>50487</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H74" s="4">
+        <v>190</v>
+      </c>
+      <c r="I74" s="4">
         <v>21</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>20</v>
-      </c>
-      <c r="B72" t="s">
-        <v>112</v>
-      </c>
-      <c r="C72" t="s">
-        <v>297</v>
-      </c>
-      <c r="D72">
-        <v>17076</v>
-      </c>
-      <c r="E72" t="s">
-        <v>85</v>
-      </c>
-      <c r="F72" t="s">
-        <v>85</v>
-      </c>
-      <c r="G72" t="s">
-        <v>67</v>
-      </c>
-      <c r="H72">
-        <v>520</v>
-      </c>
-      <c r="I72">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D75" s="4">
+        <v>1437</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H75" s="4">
+        <v>190</v>
+      </c>
+      <c r="I75" s="4">
         <v>21</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>20</v>
-      </c>
-      <c r="B73" t="s">
-        <v>113</v>
-      </c>
-      <c r="C73" t="s">
-        <v>287</v>
-      </c>
-      <c r="D73">
-        <v>32186</v>
-      </c>
-      <c r="E73" t="s">
-        <v>85</v>
-      </c>
-      <c r="F73" t="s">
-        <v>85</v>
-      </c>
-      <c r="G73" t="s">
-        <v>67</v>
-      </c>
-      <c r="H73">
-        <v>520</v>
-      </c>
-      <c r="I73">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>76</v>
-      </c>
-      <c r="B74" t="s">
-        <v>262</v>
-      </c>
-      <c r="C74" t="s">
-        <v>215</v>
-      </c>
-      <c r="D74">
-        <v>50487</v>
-      </c>
-      <c r="E74" t="s">
-        <v>85</v>
-      </c>
-      <c r="F74" t="s">
-        <v>85</v>
-      </c>
-      <c r="G74" t="s">
-        <v>67</v>
-      </c>
-      <c r="H74">
-        <v>190</v>
-      </c>
-      <c r="I74">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>76</v>
-      </c>
-      <c r="B75" t="s">
-        <v>263</v>
-      </c>
-      <c r="C75" t="s">
-        <v>215</v>
-      </c>
-      <c r="D75">
-        <v>1437</v>
-      </c>
-      <c r="E75" t="s">
-        <v>85</v>
-      </c>
-      <c r="F75" t="s">
-        <v>85</v>
-      </c>
-      <c r="G75" t="s">
-        <v>67</v>
-      </c>
-      <c r="H75">
-        <v>190</v>
-      </c>
-      <c r="I75">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>21</v>
-      </c>
-      <c r="B76" t="s">
+      <c r="B76" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="4">
         <v>4065</v>
       </c>
-      <c r="E76" t="s">
-        <v>279</v>
-      </c>
-      <c r="F76" t="str">
+      <c r="E76" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="F76" s="4" t="str">
         <f>VLOOKUP(B76,[1]colour_range_groups!$B$2:$F$140,5,FALSE)</f>
         <v>C01</v>
       </c>
-      <c r="G76" t="s">
+      <c r="G76" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H76">
+      <c r="H76" s="4">
         <v>3222</v>
       </c>
-      <c r="I76" t="s">
-        <v>269</v>
+      <c r="I76" s="4" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+      <c r="A77" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="C77" t="s">
-        <v>292</v>
-      </c>
-      <c r="D77">
+      <c r="C77" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="D77" s="4">
         <v>12632</v>
       </c>
-      <c r="E77" t="s">
-        <v>85</v>
-      </c>
-      <c r="F77" t="s">
-        <v>85</v>
-      </c>
-      <c r="G77" t="s">
-        <v>67</v>
-      </c>
-      <c r="H77">
+      <c r="E77" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H77" s="4">
         <v>22</v>
       </c>
-      <c r="I77">
+      <c r="I77" s="4">
         <v>22</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+      <c r="A78" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C78" t="s">
-        <v>285</v>
-      </c>
-      <c r="D78">
+      <c r="C78" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="D78" s="4">
         <v>26996</v>
       </c>
-      <c r="E78" t="s">
-        <v>85</v>
-      </c>
-      <c r="F78" t="s">
-        <v>85</v>
-      </c>
-      <c r="G78" t="s">
-        <v>67</v>
-      </c>
-      <c r="H78">
+      <c r="E78" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G78" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H78" s="4">
         <v>22</v>
       </c>
-      <c r="I78">
+      <c r="I78" s="4">
         <v>22</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+      <c r="A79" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C79" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D79">
+      <c r="D79" s="4">
         <v>27555</v>
       </c>
-      <c r="E79" t="s">
-        <v>279</v>
-      </c>
-      <c r="F79" t="str">
+      <c r="E79" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="F79" s="4" t="str">
         <f>VLOOKUP(B79,[1]colour_range_groups!$B$2:$F$140,5,FALSE)</f>
         <v>C12</v>
       </c>
-      <c r="G79" t="s">
+      <c r="G79" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H79">
+      <c r="H79" s="4">
         <v>1115</v>
       </c>
-      <c r="I79" t="s">
-        <v>269</v>
+      <c r="I79" s="4" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+      <c r="A80" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C80" t="s">
-        <v>284</v>
-      </c>
-      <c r="D80">
+      <c r="C80" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="D80" s="4">
         <v>2150</v>
       </c>
-      <c r="E80" t="s">
-        <v>85</v>
-      </c>
-      <c r="F80" t="s">
-        <v>85</v>
-      </c>
-      <c r="G80" t="s">
+      <c r="E80" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G80" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H80">
+      <c r="H80" s="4">
         <v>4009</v>
       </c>
-      <c r="I80">
+      <c r="I80" s="4">
         <v>828</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+      <c r="A81" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C81" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D81">
+      <c r="D81" s="4">
         <v>21847</v>
       </c>
-      <c r="E81" t="s">
-        <v>85</v>
-      </c>
-      <c r="F81" t="s">
-        <v>85</v>
-      </c>
-      <c r="G81" t="s">
+      <c r="E81" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G81" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H81">
+      <c r="H81" s="4">
         <v>4009</v>
       </c>
-      <c r="I81">
+      <c r="I81" s="4">
         <v>828</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+      <c r="A82" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C82" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D82">
+      <c r="D82" s="4">
         <v>3923</v>
       </c>
-      <c r="E82" t="s">
-        <v>279</v>
-      </c>
-      <c r="F82" t="str">
+      <c r="E82" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="F82" s="4" t="str">
         <f>VLOOKUP(B82,[1]colour_range_groups!$B$2:$F$140,5,FALSE)</f>
         <v>C05</v>
       </c>
-      <c r="G82" t="s">
+      <c r="G82" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H82">
+      <c r="H82" s="4">
         <v>4009</v>
       </c>
-      <c r="I82">
+      <c r="I82" s="4">
         <v>828</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+      <c r="A83" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C83" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="D83" s="4">
+        <v>8255</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H83" s="4">
+        <v>48</v>
+      </c>
+      <c r="I83" s="4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="D84" s="4">
+        <v>4222</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G84" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H84" s="4">
+        <v>48</v>
+      </c>
+      <c r="I84" s="4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C85" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="D83">
-        <v>8255</v>
-      </c>
-      <c r="E83" t="s">
-        <v>85</v>
-      </c>
-      <c r="F83" t="s">
-        <v>85</v>
-      </c>
-      <c r="G83" t="s">
-        <v>67</v>
-      </c>
-      <c r="H83">
+      <c r="D85" s="4">
+        <v>4966</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H85" s="4">
         <v>48</v>
       </c>
-      <c r="I83">
+      <c r="I85" s="4">
         <v>48</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>26</v>
-      </c>
-      <c r="B84" t="s">
-        <v>122</v>
-      </c>
-      <c r="C84" t="s">
-        <v>284</v>
-      </c>
-      <c r="D84">
-        <v>4222</v>
-      </c>
-      <c r="E84" t="s">
-        <v>85</v>
-      </c>
-      <c r="F84" t="s">
-        <v>85</v>
-      </c>
-      <c r="G84" t="s">
-        <v>67</v>
-      </c>
-      <c r="H84">
-        <v>48</v>
-      </c>
-      <c r="I84">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>26</v>
-      </c>
-      <c r="B85" t="s">
-        <v>123</v>
-      </c>
-      <c r="C85" t="s">
-        <v>299</v>
-      </c>
-      <c r="D85">
-        <v>4966</v>
-      </c>
-      <c r="E85" t="s">
-        <v>85</v>
-      </c>
-      <c r="F85" t="s">
-        <v>85</v>
-      </c>
-      <c r="G85" t="s">
-        <v>67</v>
-      </c>
-      <c r="H85">
-        <v>48</v>
-      </c>
-      <c r="I85">
-        <v>48</v>
-      </c>
-    </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
+      <c r="A86" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C86" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D86">
+      <c r="D86" s="4">
         <v>26574</v>
       </c>
-      <c r="E86" t="s">
-        <v>279</v>
-      </c>
-      <c r="F86" t="str">
+      <c r="E86" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="F86" s="4" t="str">
         <f>VLOOKUP(B86,[1]colour_range_groups!$B$2:$F$140,5,FALSE)</f>
         <v>C09</v>
       </c>
-      <c r="G86" t="s">
-        <v>67</v>
-      </c>
-      <c r="H86">
+      <c r="G86" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H86" s="4">
         <v>42</v>
       </c>
-      <c r="I86">
+      <c r="I86" s="4">
         <v>42</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
+      <c r="A87" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C87" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D87">
+      <c r="D87" s="4">
         <v>4703</v>
       </c>
-      <c r="E87" t="s">
-        <v>85</v>
-      </c>
-      <c r="F87" t="s">
-        <v>85</v>
-      </c>
-      <c r="G87" t="s">
-        <v>67</v>
-      </c>
-      <c r="H87">
+      <c r="E87" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H87" s="4">
         <v>48</v>
       </c>
-      <c r="I87">
+      <c r="I87" s="4">
         <v>48</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
+      <c r="A88" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C88" t="s">
-        <v>288</v>
-      </c>
-      <c r="D88">
+      <c r="C88" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="D88" s="4">
         <v>38363</v>
       </c>
-      <c r="E88" t="s">
-        <v>85</v>
-      </c>
-      <c r="F88" t="s">
-        <v>85</v>
-      </c>
-      <c r="G88" t="s">
-        <v>67</v>
-      </c>
-      <c r="H88">
+      <c r="E88" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G88" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H88" s="4">
         <v>48</v>
       </c>
-      <c r="I88">
+      <c r="I88" s="4">
         <v>48</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+      <c r="A89" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C89" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="D89" s="4">
+        <v>20089</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G89" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H89" s="4">
+        <v>61</v>
+      </c>
+      <c r="I89" s="4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D90" s="4">
+        <v>2288</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H90" s="4">
+        <v>61</v>
+      </c>
+      <c r="I90" s="4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D91" s="4">
+        <v>27115</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G91" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H91" s="4">
+        <v>422</v>
+      </c>
+      <c r="I91" s="4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D92" s="4">
+        <v>27683</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H92" s="4">
+        <v>12762</v>
+      </c>
+      <c r="I92" s="4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D93" s="4">
+        <v>2236</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G93" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H93" s="4">
+        <v>12762</v>
+      </c>
+      <c r="I93" s="4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C94" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="D89">
-        <v>20089</v>
-      </c>
-      <c r="E89" t="s">
-        <v>85</v>
-      </c>
-      <c r="F89" t="s">
-        <v>85</v>
-      </c>
-      <c r="G89" t="s">
-        <v>67</v>
-      </c>
-      <c r="H89">
+      <c r="D94" s="4">
+        <v>15949</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H94" s="4">
+        <v>12762</v>
+      </c>
+      <c r="I94" s="4">
         <v>61</v>
       </c>
-      <c r="I89">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>29</v>
-      </c>
-      <c r="B90" t="s">
-        <v>128</v>
-      </c>
-      <c r="C90" t="s">
-        <v>5</v>
-      </c>
-      <c r="D90">
-        <v>2288</v>
-      </c>
-      <c r="E90" t="s">
-        <v>85</v>
-      </c>
-      <c r="F90" t="s">
-        <v>85</v>
-      </c>
-      <c r="G90" t="s">
-        <v>67</v>
-      </c>
-      <c r="H90">
-        <v>61</v>
-      </c>
-      <c r="I90">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>30</v>
-      </c>
-      <c r="B91" t="s">
-        <v>129</v>
-      </c>
-      <c r="C91" t="s">
-        <v>7</v>
-      </c>
-      <c r="D91">
-        <v>27115</v>
-      </c>
-      <c r="E91" t="s">
-        <v>85</v>
-      </c>
-      <c r="F91" t="s">
-        <v>85</v>
-      </c>
-      <c r="G91" t="s">
-        <v>67</v>
-      </c>
-      <c r="H91">
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="D95" s="4">
+        <v>9884</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H95" s="4">
         <v>422</v>
       </c>
-      <c r="I91">
+      <c r="I95" s="4">
         <v>21</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>31</v>
-      </c>
-      <c r="B92" t="s">
-        <v>130</v>
-      </c>
-      <c r="C92" t="s">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C96" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D92">
-        <v>27683</v>
-      </c>
-      <c r="E92" t="s">
-        <v>85</v>
-      </c>
-      <c r="F92" t="s">
-        <v>85</v>
-      </c>
-      <c r="G92" t="s">
-        <v>67</v>
-      </c>
-      <c r="H92">
-        <v>12762</v>
-      </c>
-      <c r="I92" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>31</v>
-      </c>
-      <c r="B93" t="s">
-        <v>131</v>
-      </c>
-      <c r="C93" t="s">
+      <c r="D96" s="4">
+        <v>29895</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G96" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H96" s="4">
+        <v>422</v>
+      </c>
+      <c r="I96" s="4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C97" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D93">
-        <v>2236</v>
-      </c>
-      <c r="E93" t="s">
-        <v>85</v>
-      </c>
-      <c r="F93" t="s">
-        <v>85</v>
-      </c>
-      <c r="G93" t="s">
-        <v>67</v>
-      </c>
-      <c r="H93">
-        <v>12762</v>
-      </c>
-      <c r="I93" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>31</v>
-      </c>
-      <c r="B94" t="s">
-        <v>132</v>
-      </c>
-      <c r="C94" t="s">
+      <c r="D97" s="4">
+        <v>8394</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G97" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H97" s="4">
+        <v>422</v>
+      </c>
+      <c r="I97" s="4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C98" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="D94">
-        <v>15949</v>
-      </c>
-      <c r="E94" t="s">
-        <v>85</v>
-      </c>
-      <c r="F94" t="s">
-        <v>85</v>
-      </c>
-      <c r="G94" t="s">
-        <v>67</v>
-      </c>
-      <c r="H94">
-        <v>12762</v>
-      </c>
-      <c r="I94" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>32</v>
-      </c>
-      <c r="B95" t="s">
-        <v>133</v>
-      </c>
-      <c r="C95" t="s">
-        <v>284</v>
-      </c>
-      <c r="D95">
-        <v>9884</v>
-      </c>
-      <c r="E95" t="s">
-        <v>85</v>
-      </c>
-      <c r="F95" t="s">
-        <v>85</v>
-      </c>
-      <c r="G95" t="s">
-        <v>67</v>
-      </c>
-      <c r="H95">
+      <c r="D98" s="4">
+        <v>14700</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G98" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H98" s="4">
         <v>422</v>
       </c>
-      <c r="I95">
+      <c r="I98" s="4">
         <v>21</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>32</v>
-      </c>
-      <c r="B96" t="s">
-        <v>134</v>
-      </c>
-      <c r="C96" t="s">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D99" s="4">
+        <v>1503</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G99" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H99" s="4">
+        <v>6964</v>
+      </c>
+      <c r="I99" s="4">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="D100" s="4">
+        <v>12920</v>
+      </c>
+      <c r="E100" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G100" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H100" s="4">
+        <v>6964</v>
+      </c>
+      <c r="I100" s="4">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="D101" s="4">
+        <v>28083</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G101" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H101" s="4">
+        <v>830</v>
+      </c>
+      <c r="I101" s="4">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="D102" s="4">
+        <v>2534</v>
+      </c>
+      <c r="E102" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G102" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H102" s="4">
+        <v>830</v>
+      </c>
+      <c r="I102" s="4">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="D103" s="4">
+        <v>5507</v>
+      </c>
+      <c r="E103" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G103" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H103" s="4">
+        <v>830</v>
+      </c>
+      <c r="I103" s="4">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D104" s="4">
+        <v>2033</v>
+      </c>
+      <c r="E104" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G104" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H104" s="4">
+        <v>42</v>
+      </c>
+      <c r="I104" s="4">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="D105" s="4">
+        <v>22779</v>
+      </c>
+      <c r="E105" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G105" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H105" s="4">
+        <v>42</v>
+      </c>
+      <c r="I105" s="4">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C106" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D96">
-        <v>29895</v>
-      </c>
-      <c r="E96" t="s">
-        <v>85</v>
-      </c>
-      <c r="F96" t="s">
-        <v>85</v>
-      </c>
-      <c r="G96" t="s">
-        <v>67</v>
-      </c>
-      <c r="H96">
-        <v>422</v>
-      </c>
-      <c r="I96">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>32</v>
-      </c>
-      <c r="B97" t="s">
-        <v>135</v>
-      </c>
-      <c r="C97" t="s">
-        <v>17</v>
-      </c>
-      <c r="D97">
-        <v>8394</v>
-      </c>
-      <c r="E97" t="s">
-        <v>85</v>
-      </c>
-      <c r="F97" t="s">
-        <v>85</v>
-      </c>
-      <c r="G97" t="s">
-        <v>67</v>
-      </c>
-      <c r="H97">
-        <v>422</v>
-      </c>
-      <c r="I97">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>32</v>
-      </c>
-      <c r="B98" t="s">
-        <v>136</v>
-      </c>
-      <c r="C98" t="s">
-        <v>298</v>
-      </c>
-      <c r="D98">
-        <v>14700</v>
-      </c>
-      <c r="E98" t="s">
-        <v>85</v>
-      </c>
-      <c r="F98" t="s">
-        <v>85</v>
-      </c>
-      <c r="G98" t="s">
-        <v>67</v>
-      </c>
-      <c r="H98">
-        <v>422</v>
-      </c>
-      <c r="I98">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>33</v>
-      </c>
-      <c r="B99" t="s">
-        <v>137</v>
-      </c>
-      <c r="C99" t="s">
-        <v>17</v>
-      </c>
-      <c r="D99">
-        <v>1503</v>
-      </c>
-      <c r="E99" t="s">
-        <v>85</v>
-      </c>
-      <c r="F99" t="s">
-        <v>85</v>
-      </c>
-      <c r="G99" t="s">
-        <v>67</v>
-      </c>
-      <c r="H99">
-        <v>6964</v>
-      </c>
-      <c r="I99">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>33</v>
-      </c>
-      <c r="B100" t="s">
-        <v>138</v>
-      </c>
-      <c r="C100" t="s">
-        <v>297</v>
-      </c>
-      <c r="D100">
-        <v>12920</v>
-      </c>
-      <c r="E100" t="s">
-        <v>85</v>
-      </c>
-      <c r="F100" t="s">
-        <v>85</v>
-      </c>
-      <c r="G100" t="s">
-        <v>67</v>
-      </c>
-      <c r="H100">
-        <v>6964</v>
-      </c>
-      <c r="I100">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>34</v>
-      </c>
-      <c r="B101" t="s">
-        <v>139</v>
-      </c>
-      <c r="C101" t="s">
-        <v>293</v>
-      </c>
-      <c r="D101">
-        <v>28083</v>
-      </c>
-      <c r="E101" t="s">
-        <v>85</v>
-      </c>
-      <c r="F101" t="s">
-        <v>85</v>
-      </c>
-      <c r="G101" t="s">
-        <v>65</v>
-      </c>
-      <c r="H101">
-        <v>830</v>
-      </c>
-      <c r="I101">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>34</v>
-      </c>
-      <c r="B102" t="s">
-        <v>140</v>
-      </c>
-      <c r="C102" t="s">
-        <v>300</v>
-      </c>
-      <c r="D102">
-        <v>2534</v>
-      </c>
-      <c r="E102" t="s">
-        <v>85</v>
-      </c>
-      <c r="F102" t="s">
-        <v>85</v>
-      </c>
-      <c r="G102" t="s">
-        <v>65</v>
-      </c>
-      <c r="H102">
-        <v>830</v>
-      </c>
-      <c r="I102">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>34</v>
-      </c>
-      <c r="B103" t="s">
-        <v>141</v>
-      </c>
-      <c r="C103" t="s">
-        <v>284</v>
-      </c>
-      <c r="D103">
-        <v>5507</v>
-      </c>
-      <c r="E103" t="s">
-        <v>85</v>
-      </c>
-      <c r="F103" t="s">
-        <v>85</v>
-      </c>
-      <c r="G103" t="s">
-        <v>65</v>
-      </c>
-      <c r="H103">
-        <v>830</v>
-      </c>
-      <c r="I103">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>35</v>
-      </c>
-      <c r="B104" t="s">
-        <v>142</v>
-      </c>
-      <c r="C104" t="s">
-        <v>143</v>
-      </c>
-      <c r="D104">
-        <v>2033</v>
-      </c>
-      <c r="E104" t="s">
-        <v>85</v>
-      </c>
-      <c r="F104" t="s">
-        <v>85</v>
-      </c>
-      <c r="G104" t="s">
-        <v>67</v>
-      </c>
-      <c r="H104">
-        <v>42</v>
-      </c>
-      <c r="I104">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>35</v>
-      </c>
-      <c r="B105" t="s">
-        <v>144</v>
-      </c>
-      <c r="C105" t="s">
-        <v>294</v>
-      </c>
-      <c r="D105">
-        <v>22779</v>
-      </c>
-      <c r="E105" t="s">
-        <v>85</v>
-      </c>
-      <c r="F105" t="s">
-        <v>85</v>
-      </c>
-      <c r="G105" t="s">
-        <v>67</v>
-      </c>
-      <c r="H105">
-        <v>42</v>
-      </c>
-      <c r="I105">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>35</v>
-      </c>
-      <c r="B106" t="s">
-        <v>145</v>
-      </c>
-      <c r="C106" t="s">
-        <v>13</v>
-      </c>
-      <c r="D106">
+      <c r="D106" s="4">
         <v>26195</v>
       </c>
-      <c r="E106" t="s">
-        <v>279</v>
-      </c>
-      <c r="F106" t="str">
+      <c r="E106" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="F106" s="4" t="str">
         <f>VLOOKUP(B106,[1]colour_range_groups!$B$2:$F$140,5,FALSE)</f>
         <v>C09</v>
       </c>
-      <c r="G106" t="s">
-        <v>67</v>
-      </c>
-      <c r="H106">
+      <c r="G106" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H106" s="4">
         <v>42</v>
       </c>
-      <c r="I106">
+      <c r="I106" s="4">
         <v>42</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
+      <c r="A107" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="C107" t="s">
+      <c r="C107" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D107">
+      <c r="D107" s="4">
         <v>30065</v>
       </c>
-      <c r="E107" t="s">
-        <v>279</v>
-      </c>
-      <c r="F107" t="str">
+      <c r="E107" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="F107" s="4" t="str">
         <f>VLOOKUP(B107,[1]colour_range_groups!$B$2:$F$140,5,FALSE)</f>
         <v>C11</v>
       </c>
-      <c r="G107" t="s">
-        <v>67</v>
-      </c>
-      <c r="H107">
+      <c r="G107" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H107" s="4">
         <v>42</v>
       </c>
-      <c r="I107">
+      <c r="I107" s="4">
         <v>42</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
+      <c r="A108" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="C108" t="s">
+      <c r="C108" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="D108" s="4">
+        <v>14549</v>
+      </c>
+      <c r="E108" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F108" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G108" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H108" s="4">
+        <v>3232</v>
+      </c>
+      <c r="I108" s="4">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A109" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D109" s="4">
+        <v>2291</v>
+      </c>
+      <c r="E109" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F109" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G109" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H109" s="4">
+        <v>3232</v>
+      </c>
+      <c r="I109" s="4">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C110" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="D108">
-        <v>14549</v>
-      </c>
-      <c r="E108" t="s">
-        <v>85</v>
-      </c>
-      <c r="F108" t="s">
-        <v>85</v>
-      </c>
-      <c r="G108" t="s">
+      <c r="D110" s="4">
+        <v>3384</v>
+      </c>
+      <c r="E110" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G110" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H108">
+      <c r="H110" s="4">
         <v>3232</v>
       </c>
-      <c r="I108">
+      <c r="I110" s="4">
         <v>828</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>37</v>
-      </c>
-      <c r="B109" t="s">
-        <v>148</v>
-      </c>
-      <c r="C109" t="s">
-        <v>5</v>
-      </c>
-      <c r="D109">
-        <v>2291</v>
-      </c>
-      <c r="E109" t="s">
-        <v>85</v>
-      </c>
-      <c r="F109" t="s">
-        <v>85</v>
-      </c>
-      <c r="G109" t="s">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D111" s="4">
+        <v>18419</v>
+      </c>
+      <c r="E111" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G111" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H109">
-        <v>3232</v>
-      </c>
-      <c r="I109">
+      <c r="H111" s="4">
+        <v>14595</v>
+      </c>
+      <c r="I111" s="4">
         <v>828</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>37</v>
-      </c>
-      <c r="B110" t="s">
-        <v>149</v>
-      </c>
-      <c r="C110" t="s">
-        <v>302</v>
-      </c>
-      <c r="D110">
-        <v>3384</v>
-      </c>
-      <c r="E110" t="s">
-        <v>85</v>
-      </c>
-      <c r="F110" t="s">
-        <v>85</v>
-      </c>
-      <c r="G110" t="s">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="D112" s="4">
+        <v>4199</v>
+      </c>
+      <c r="E112" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F112" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G112" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H110">
-        <v>3232</v>
-      </c>
-      <c r="I110">
+      <c r="H112" s="4">
+        <v>14595</v>
+      </c>
+      <c r="I112" s="4">
         <v>828</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>38</v>
-      </c>
-      <c r="B111" t="s">
-        <v>150</v>
-      </c>
-      <c r="C111" t="s">
-        <v>92</v>
-      </c>
-      <c r="D111">
-        <v>18419</v>
-      </c>
-      <c r="E111" t="s">
-        <v>85</v>
-      </c>
-      <c r="F111" t="s">
-        <v>85</v>
-      </c>
-      <c r="G111" t="s">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A113" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D113" s="4">
+        <v>2313</v>
+      </c>
+      <c r="E113" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G113" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H111">
-        <v>14595</v>
-      </c>
-      <c r="I111" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>38</v>
-      </c>
-      <c r="B112" t="s">
-        <v>151</v>
-      </c>
-      <c r="C112" t="s">
-        <v>284</v>
-      </c>
-      <c r="D112">
-        <v>4199</v>
-      </c>
-      <c r="E112" t="s">
-        <v>85</v>
-      </c>
-      <c r="F112" t="s">
-        <v>85</v>
-      </c>
-      <c r="G112" t="s">
+      <c r="H113" s="4">
+        <v>900</v>
+      </c>
+      <c r="I113" s="4" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A114" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="D114" s="4">
+        <v>10918</v>
+      </c>
+      <c r="E114" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G114" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H112">
-        <v>14595</v>
-      </c>
-      <c r="I112" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
+      <c r="H114" s="4">
+        <v>900</v>
+      </c>
+      <c r="I114" s="4" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A115" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B113" t="s">
-        <v>152</v>
-      </c>
-      <c r="C113" t="s">
-        <v>143</v>
-      </c>
-      <c r="D113">
-        <v>2313</v>
-      </c>
-      <c r="E113" t="s">
-        <v>85</v>
-      </c>
-      <c r="F113" t="s">
-        <v>85</v>
-      </c>
-      <c r="G113" t="s">
+      <c r="B115" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="D115" s="4">
+        <v>18335</v>
+      </c>
+      <c r="E115" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G115" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H113">
+      <c r="H115" s="4">
         <v>900</v>
       </c>
-      <c r="I113" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
+      <c r="I115" s="4" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A116" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B114" t="s">
-        <v>153</v>
-      </c>
-      <c r="C114" t="s">
-        <v>284</v>
-      </c>
-      <c r="D114">
-        <v>10918</v>
-      </c>
-      <c r="E114" t="s">
-        <v>85</v>
-      </c>
-      <c r="F114" t="s">
-        <v>85</v>
-      </c>
-      <c r="G114" t="s">
+      <c r="B116" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="D116" s="4">
+        <v>2171</v>
+      </c>
+      <c r="E116" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G116" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H114">
+      <c r="H116" s="4">
         <v>900</v>
       </c>
-      <c r="I114" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
+      <c r="I116" s="4" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A117" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B115" t="s">
-        <v>154</v>
-      </c>
-      <c r="C115" t="s">
-        <v>290</v>
-      </c>
-      <c r="D115">
-        <v>18335</v>
-      </c>
-      <c r="E115" t="s">
-        <v>85</v>
-      </c>
-      <c r="F115" t="s">
-        <v>85</v>
-      </c>
-      <c r="G115" t="s">
+      <c r="B117" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="D117" s="4">
+        <v>7481</v>
+      </c>
+      <c r="E117" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G117" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H115">
+      <c r="H117" s="4">
         <v>900</v>
       </c>
-      <c r="I115" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
+      <c r="I117" s="4" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A118" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B116" t="s">
-        <v>155</v>
-      </c>
-      <c r="C116" t="s">
-        <v>302</v>
-      </c>
-      <c r="D116">
-        <v>2171</v>
-      </c>
-      <c r="E116" t="s">
-        <v>85</v>
-      </c>
-      <c r="F116" t="s">
-        <v>85</v>
-      </c>
-      <c r="G116" t="s">
+      <c r="B118" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="D118" s="4">
+        <v>14754</v>
+      </c>
+      <c r="E118" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G118" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H116">
+      <c r="H118" s="4">
         <v>900</v>
       </c>
-      <c r="I116" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
+      <c r="I118" s="4" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A119" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B117" t="s">
-        <v>156</v>
-      </c>
-      <c r="C117" t="s">
-        <v>295</v>
-      </c>
-      <c r="D117">
-        <v>7481</v>
-      </c>
-      <c r="E117" t="s">
-        <v>85</v>
-      </c>
-      <c r="F117" t="s">
-        <v>85</v>
-      </c>
-      <c r="G117" t="s">
+      <c r="B119" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="D119" s="4">
+        <v>15356</v>
+      </c>
+      <c r="E119" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G119" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H117">
+      <c r="H119" s="4">
         <v>900</v>
       </c>
-      <c r="I117" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
+      <c r="I119" s="4" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A120" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B118" t="s">
-        <v>157</v>
-      </c>
-      <c r="C118" t="s">
-        <v>301</v>
-      </c>
-      <c r="D118">
-        <v>14754</v>
-      </c>
-      <c r="E118" t="s">
-        <v>85</v>
-      </c>
-      <c r="F118" t="s">
-        <v>85</v>
-      </c>
-      <c r="G118" t="s">
-        <v>65</v>
-      </c>
-      <c r="H118">
-        <v>900</v>
-      </c>
-      <c r="I118" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>39</v>
-      </c>
-      <c r="B119" t="s">
-        <v>158</v>
-      </c>
-      <c r="C119" t="s">
-        <v>297</v>
-      </c>
-      <c r="D119">
-        <v>15356</v>
-      </c>
-      <c r="E119" t="s">
-        <v>85</v>
-      </c>
-      <c r="F119" t="s">
-        <v>85</v>
-      </c>
-      <c r="G119" t="s">
-        <v>65</v>
-      </c>
-      <c r="H119">
-        <v>900</v>
-      </c>
-      <c r="I119" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
-        <v>39</v>
-      </c>
-      <c r="B120" t="s">
+      <c r="B120" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="C120" t="s">
+      <c r="C120" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D120">
+      <c r="D120" s="4">
         <v>2428</v>
       </c>
-      <c r="E120" t="s">
-        <v>279</v>
-      </c>
-      <c r="F120" t="str">
+      <c r="E120" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="F120" s="4" t="str">
         <f>VLOOKUP(B120,[1]colour_range_groups!$B$2:$F$140,5,FALSE)</f>
         <v>C07</v>
       </c>
-      <c r="G120" t="s">
+      <c r="G120" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H120">
+      <c r="H120" s="4">
         <v>900</v>
       </c>
-      <c r="I120" t="s">
-        <v>269</v>
+      <c r="I120" s="4" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
+      <c r="A121" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="C121" t="s">
-        <v>299</v>
-      </c>
-      <c r="D121">
+      <c r="C121" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="D121" s="4">
         <v>1639</v>
       </c>
-      <c r="E121" t="s">
-        <v>85</v>
-      </c>
-      <c r="F121" t="s">
-        <v>85</v>
-      </c>
-      <c r="G121" t="s">
+      <c r="E121" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G121" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H121">
+      <c r="H121" s="4">
         <v>5734</v>
       </c>
-      <c r="I121">
+      <c r="I121" s="4">
         <v>828</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
+      <c r="A122" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="C122" t="s">
+      <c r="C122" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D122">
+      <c r="D122" s="4">
         <v>22678</v>
       </c>
-      <c r="E122" t="s">
-        <v>85</v>
-      </c>
-      <c r="F122" t="s">
-        <v>85</v>
-      </c>
-      <c r="G122" t="s">
-        <v>67</v>
-      </c>
-      <c r="H122">
+      <c r="E122" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F122" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G122" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H122" s="4">
         <v>14186</v>
       </c>
-      <c r="I122" t="s">
-        <v>269</v>
+      <c r="I122" s="4">
+        <v>52</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
+      <c r="A123" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="C123" t="s">
-        <v>282</v>
-      </c>
-      <c r="D123">
+      <c r="C123" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="D123" s="4">
         <v>20532</v>
       </c>
-      <c r="E123" t="s">
-        <v>85</v>
-      </c>
-      <c r="F123" t="s">
-        <v>85</v>
-      </c>
-      <c r="G123" t="s">
-        <v>67</v>
-      </c>
-      <c r="H123">
+      <c r="E123" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G123" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H123" s="4">
         <v>14186</v>
       </c>
-      <c r="I123" t="s">
-        <v>269</v>
+      <c r="I123" s="4">
+        <v>52</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
+      <c r="A124" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="C124" t="s">
-        <v>284</v>
-      </c>
-      <c r="D124">
+      <c r="C124" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="D124" s="4">
         <v>10040</v>
       </c>
-      <c r="E124" t="s">
-        <v>85</v>
-      </c>
-      <c r="F124" t="s">
-        <v>85</v>
-      </c>
-      <c r="G124" t="s">
-        <v>67</v>
-      </c>
-      <c r="H124">
+      <c r="E124" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F124" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G124" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H124" s="4">
         <v>14186</v>
       </c>
-      <c r="I124" t="s">
-        <v>269</v>
+      <c r="I124" s="4">
+        <v>52</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
+      <c r="A125" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="C125" t="s">
+      <c r="C125" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D125">
+      <c r="D125" s="4">
         <v>9848</v>
       </c>
-      <c r="E125" t="s">
-        <v>85</v>
-      </c>
-      <c r="F125" t="s">
-        <v>85</v>
-      </c>
-      <c r="G125" t="s">
-        <v>67</v>
-      </c>
-      <c r="H125">
+      <c r="E125" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F125" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G125" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H125" s="4">
         <v>14186</v>
       </c>
-      <c r="I125" t="s">
-        <v>269</v>
+      <c r="I125" s="4">
+        <v>52</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
+      <c r="A126" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="C126" t="s">
-        <v>296</v>
-      </c>
-      <c r="D126">
+      <c r="C126" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="D126" s="4">
         <v>18065</v>
       </c>
-      <c r="E126" t="s">
-        <v>85</v>
-      </c>
-      <c r="F126" t="s">
-        <v>85</v>
-      </c>
-      <c r="G126" t="s">
+      <c r="E126" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F126" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G126" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H126">
+      <c r="H126" s="4">
         <v>900</v>
       </c>
-      <c r="I126" t="s">
-        <v>269</v>
+      <c r="I126" s="4" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
+      <c r="A127" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="C127" t="s">
+      <c r="C127" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D127">
+      <c r="D127" s="4">
         <v>3770</v>
       </c>
-      <c r="E127" t="s">
-        <v>85</v>
-      </c>
-      <c r="F127" t="s">
-        <v>85</v>
-      </c>
-      <c r="G127" t="s">
+      <c r="E127" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G127" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H127">
+      <c r="H127" s="4">
         <v>900</v>
       </c>
-      <c r="I127" t="s">
-        <v>269</v>
+      <c r="I127" s="4" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
+      <c r="A128" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="C128" t="s">
+      <c r="C128" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D128">
+      <c r="D128" s="4">
         <v>3721</v>
       </c>
-      <c r="E128" t="s">
-        <v>85</v>
-      </c>
-      <c r="F128" t="s">
-        <v>85</v>
-      </c>
-      <c r="G128" t="s">
+      <c r="E128" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G128" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H128">
+      <c r="H128" s="4">
         <v>900</v>
       </c>
-      <c r="I128" t="s">
-        <v>269</v>
+      <c r="I128" s="4" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
+      <c r="A129" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="C129" t="s">
+      <c r="C129" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D129">
+      <c r="D129" s="4">
         <v>2428</v>
       </c>
-      <c r="E129" t="s">
-        <v>279</v>
-      </c>
-      <c r="F129" t="str">
+      <c r="E129" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="F129" s="4" t="str">
         <f>VLOOKUP(B129,[1]colour_range_groups!$B$2:$F$140,5,FALSE)</f>
         <v>C07</v>
       </c>
-      <c r="G129" t="s">
+      <c r="G129" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H129">
+      <c r="H129" s="4">
         <v>900</v>
       </c>
-      <c r="I129" t="s">
-        <v>269</v>
-      </c>
-      <c r="J129" t="s">
-        <v>274</v>
+      <c r="I129" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="J129" s="4" t="s">
+        <v>273</v>
       </c>
       <c r="K129" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
+      <c r="A130" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C130" t="s">
-        <v>290</v>
-      </c>
-      <c r="D130">
+      <c r="C130" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="D130" s="4">
         <v>18335</v>
       </c>
-      <c r="E130" t="s">
-        <v>85</v>
-      </c>
-      <c r="F130" t="s">
-        <v>85</v>
-      </c>
-      <c r="G130" t="s">
+      <c r="E130" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F130" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G130" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H130">
+      <c r="H130" s="4">
         <v>900</v>
       </c>
-      <c r="I130" t="s">
-        <v>269</v>
+      <c r="I130" s="4" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
+      <c r="A131" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="C131" t="s">
-        <v>295</v>
-      </c>
-      <c r="D131">
+      <c r="C131" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="D131" s="4">
         <v>7622</v>
       </c>
-      <c r="E131" t="s">
-        <v>85</v>
-      </c>
-      <c r="F131" t="s">
-        <v>85</v>
-      </c>
-      <c r="G131" t="s">
+      <c r="E131" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F131" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G131" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H131">
+      <c r="H131" s="4">
         <v>900</v>
       </c>
-      <c r="I131" t="s">
-        <v>269</v>
+      <c r="I131" s="4" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
+      <c r="A132" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="C132" t="s">
+      <c r="C132" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D132">
+      <c r="D132" s="4">
         <v>36277</v>
       </c>
-      <c r="E132" t="s">
-        <v>279</v>
-      </c>
-      <c r="F132" t="str">
+      <c r="E132" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="F132" s="4" t="str">
         <f>VLOOKUP(B132,[1]colour_range_groups!$B$2:$F$140,5,FALSE)</f>
         <v>C14</v>
       </c>
-      <c r="G132" t="s">
+      <c r="G132" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H132">
+      <c r="H132" s="4">
         <v>900</v>
       </c>
-      <c r="I132" t="s">
-        <v>269</v>
+      <c r="I132" s="4" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
+      <c r="A133" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="C133" t="s">
+      <c r="C133" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D133">
+      <c r="D133" s="4">
         <v>8529</v>
       </c>
-      <c r="E133" t="s">
-        <v>85</v>
-      </c>
-      <c r="F133" t="s">
-        <v>85</v>
-      </c>
-      <c r="G133" t="s">
+      <c r="E133" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F133" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G133" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H133">
+      <c r="H133" s="4">
         <v>829</v>
       </c>
-      <c r="I133">
+      <c r="I133" s="4">
         <v>828</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
+      <c r="A134" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="C134" t="s">
+      <c r="C134" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D134">
+      <c r="D134" s="4">
         <v>29036</v>
       </c>
-      <c r="E134" t="s">
-        <v>85</v>
-      </c>
-      <c r="F134" t="s">
-        <v>85</v>
-      </c>
-      <c r="G134" t="s">
+      <c r="E134" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F134" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G134" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H134">
+      <c r="H134" s="4">
         <v>829</v>
       </c>
-      <c r="I134">
+      <c r="I134" s="4">
         <v>828</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
+      <c r="A135" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="C135" t="s">
-        <v>301</v>
-      </c>
-      <c r="D135">
+      <c r="C135" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="D135" s="4">
         <v>14528</v>
       </c>
-      <c r="E135" t="s">
-        <v>85</v>
-      </c>
-      <c r="F135" t="s">
-        <v>85</v>
-      </c>
-      <c r="G135" t="s">
+      <c r="E135" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F135" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G135" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H135">
+      <c r="H135" s="4">
         <v>829</v>
       </c>
-      <c r="I135">
+      <c r="I135" s="4">
         <v>828</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
+      <c r="A136" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="C136" t="s">
+      <c r="C136" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D136">
+      <c r="D136" s="4">
         <v>2427</v>
       </c>
-      <c r="E136" t="s">
-        <v>279</v>
-      </c>
-      <c r="F136" t="str">
+      <c r="E136" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="F136" s="4" t="str">
         <f>VLOOKUP(B136,[1]colour_range_groups!$B$2:$F$140,5,FALSE)</f>
         <v>C07</v>
       </c>
-      <c r="G136" t="s">
+      <c r="G136" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H136">
+      <c r="H136" s="4">
         <v>829</v>
       </c>
-      <c r="I136">
+      <c r="I136" s="4">
         <v>828</v>
       </c>
-      <c r="J136" t="s">
-        <v>275</v>
+      <c r="J136" s="4" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
+      <c r="A137" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="C137" t="s">
+      <c r="C137" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D137">
+      <c r="D137" s="4">
         <v>37369</v>
       </c>
-      <c r="E137" t="s">
-        <v>85</v>
-      </c>
-      <c r="F137" t="s">
-        <v>85</v>
-      </c>
-      <c r="G137" t="s">
-        <v>67</v>
-      </c>
-      <c r="H137">
+      <c r="E137" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F137" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G137" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H137" s="4">
         <v>53</v>
       </c>
-      <c r="I137">
+      <c r="I137" s="4">
         <v>21</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
+      <c r="A138" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="C138" t="s">
+      <c r="C138" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D138">
+      <c r="D138" s="4">
         <v>28059</v>
       </c>
-      <c r="E138" t="s">
-        <v>279</v>
-      </c>
-      <c r="F138" t="str">
+      <c r="E138" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="F138" s="4" t="str">
         <f>VLOOKUP(B138,[1]colour_range_groups!$B$2:$F$140,5,FALSE)</f>
         <v>C11</v>
       </c>
-      <c r="G138" t="s">
-        <v>67</v>
-      </c>
-      <c r="H138">
+      <c r="G138" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H138" s="4">
         <v>53</v>
       </c>
-      <c r="I138">
+      <c r="I138" s="4">
         <v>21</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
+      <c r="A139" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="C139" t="s">
+      <c r="C139" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D139">
+      <c r="D139" s="4">
         <v>1690</v>
       </c>
-      <c r="E139" t="s">
-        <v>85</v>
-      </c>
-      <c r="F139" t="s">
-        <v>85</v>
-      </c>
-      <c r="G139" t="s">
-        <v>67</v>
-      </c>
-      <c r="H139">
+      <c r="E139" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F139" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G139" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H139" s="4">
         <v>45</v>
       </c>
-      <c r="I139">
+      <c r="I139" s="4">
         <v>45</v>
       </c>
-      <c r="J139" t="s">
-        <v>276</v>
+      <c r="J139" s="4" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
+      <c r="A140" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="C140" t="s">
+      <c r="C140" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D140">
+      <c r="D140" s="4">
         <v>3605</v>
       </c>
-      <c r="E140" t="s">
-        <v>85</v>
-      </c>
-      <c r="F140" t="s">
-        <v>85</v>
-      </c>
-      <c r="G140" t="s">
-        <v>67</v>
-      </c>
-      <c r="H140">
+      <c r="E140" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F140" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G140" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H140" s="4">
         <v>677</v>
       </c>
-      <c r="I140">
+      <c r="I140" s="4">
         <v>677</v>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
+      <c r="A141" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="C141" t="s">
+      <c r="C141" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D141">
+      <c r="D141" s="4">
         <v>5381</v>
       </c>
-      <c r="E141" t="s">
-        <v>279</v>
-      </c>
-      <c r="F141" t="str">
+      <c r="E141" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="F141" s="4" t="str">
         <f>VLOOKUP(B141,[1]colour_range_groups!$B$2:$F$140,5,FALSE)</f>
         <v>C04</v>
       </c>
-      <c r="G141" t="s">
-        <v>67</v>
-      </c>
-      <c r="H141">
+      <c r="G141" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H141" s="4">
         <v>5647</v>
       </c>
-      <c r="I141">
+      <c r="I141" s="4">
         <v>692</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
+      <c r="A142" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B142" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="C142" t="s">
+      <c r="C142" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D142">
+      <c r="D142" s="4">
         <v>45668</v>
       </c>
-      <c r="E142" t="s">
-        <v>279</v>
-      </c>
-      <c r="F142" t="str">
+      <c r="E142" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="F142" s="4" t="str">
         <f>VLOOKUP(B142,[1]colour_range_groups!$B$2:$F$140,5,FALSE)</f>
         <v>C08</v>
       </c>
-      <c r="G142" t="s">
-        <v>67</v>
-      </c>
-      <c r="H142">
+      <c r="G142" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H142" s="4">
         <v>48</v>
       </c>
-      <c r="I142">
+      <c r="I142" s="4">
         <v>48</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
+      <c r="A143" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B143" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C143" t="s">
+      <c r="C143" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D143">
+      <c r="D143" s="4">
         <v>4173</v>
       </c>
-      <c r="E143" t="s">
-        <v>85</v>
-      </c>
-      <c r="F143" t="s">
-        <v>85</v>
-      </c>
-      <c r="G143" t="s">
+      <c r="E143" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F143" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G143" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H143">
+      <c r="H143" s="4">
         <v>8926</v>
       </c>
-      <c r="I143">
+      <c r="I143" s="4">
         <v>828</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
+      <c r="A144" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B144" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="C144" t="s">
-        <v>294</v>
-      </c>
-      <c r="D144">
+      <c r="C144" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="D144" s="4">
         <v>22538</v>
       </c>
-      <c r="E144" t="s">
-        <v>85</v>
-      </c>
-      <c r="F144" t="s">
-        <v>85</v>
-      </c>
-      <c r="G144" t="s">
+      <c r="E144" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F144" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G144" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H144">
+      <c r="H144" s="4">
         <v>8926</v>
       </c>
-      <c r="I144">
+      <c r="I144" s="4">
         <v>828</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
+      <c r="A145" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B145" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="C145" t="s">
+      <c r="C145" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D145">
+      <c r="D145" s="4">
         <v>9896</v>
       </c>
-      <c r="E145" t="s">
-        <v>85</v>
-      </c>
-      <c r="F145" t="s">
-        <v>85</v>
-      </c>
-      <c r="G145" t="s">
-        <v>67</v>
-      </c>
-      <c r="H145">
+      <c r="E145" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F145" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G145" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H145" s="4">
         <v>583</v>
       </c>
-      <c r="I145">
+      <c r="I145" s="4">
         <v>45</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
+      <c r="A146" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="C146" t="s">
+      <c r="C146" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D146">
+      <c r="D146" s="4">
         <v>1979</v>
       </c>
-      <c r="E146" t="s">
-        <v>85</v>
-      </c>
-      <c r="F146" t="s">
-        <v>85</v>
-      </c>
-      <c r="G146" t="s">
-        <v>67</v>
-      </c>
-      <c r="H146">
+      <c r="E146" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F146" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G146" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H146" s="4">
         <v>583</v>
       </c>
-      <c r="I146">
+      <c r="I146" s="4">
         <v>45</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
+      <c r="A147" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B147" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="C147" t="s">
+      <c r="C147" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D147">
+      <c r="D147" s="4">
         <v>27311</v>
       </c>
-      <c r="E147" t="s">
-        <v>85</v>
-      </c>
-      <c r="F147" t="s">
-        <v>85</v>
-      </c>
-      <c r="G147" t="s">
-        <v>67</v>
-      </c>
-      <c r="H147">
+      <c r="E147" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F147" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G147" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H147" s="4">
         <v>2392</v>
       </c>
-      <c r="I147">
+      <c r="I147" s="4">
         <v>52</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
+      <c r="A148" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="C148" t="s">
+      <c r="C148" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D148">
+      <c r="D148" s="4">
         <v>20683</v>
       </c>
-      <c r="E148" t="s">
-        <v>85</v>
-      </c>
-      <c r="F148" t="s">
-        <v>85</v>
-      </c>
-      <c r="G148" t="s">
-        <v>67</v>
-      </c>
-      <c r="H148">
+      <c r="E148" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F148" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G148" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H148" s="4">
         <v>61</v>
       </c>
-      <c r="I148">
+      <c r="I148" s="4">
         <v>61</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
+      <c r="A149" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B149" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="C149" t="s">
+      <c r="C149" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D149">
+      <c r="D149" s="4">
         <v>11764</v>
       </c>
-      <c r="E149" t="s">
-        <v>85</v>
-      </c>
-      <c r="F149" t="s">
-        <v>85</v>
-      </c>
-      <c r="G149" t="s">
-        <v>67</v>
-      </c>
-      <c r="H149">
+      <c r="E149" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F149" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G149" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H149" s="4">
         <v>51</v>
       </c>
-      <c r="I149">
+      <c r="I149" s="4">
         <v>443</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
+      <c r="A150" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B150" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="C150" t="s">
-        <v>282</v>
-      </c>
-      <c r="D150">
+      <c r="C150" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="D150" s="4">
         <v>24214</v>
       </c>
-      <c r="E150" t="s">
-        <v>85</v>
-      </c>
-      <c r="F150" t="s">
-        <v>85</v>
-      </c>
-      <c r="G150" t="s">
-        <v>67</v>
-      </c>
-      <c r="H150">
+      <c r="E150" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F150" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G150" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H150" s="4">
         <v>51</v>
       </c>
-      <c r="I150">
+      <c r="I150" s="4">
         <v>443</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
+      <c r="A151" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B151" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="C151" t="s">
+      <c r="C151" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D151">
+      <c r="D151" s="4">
         <v>28972</v>
       </c>
-      <c r="E151" t="s">
-        <v>279</v>
-      </c>
-      <c r="F151" t="str">
+      <c r="E151" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="F151" s="4" t="str">
         <f>VLOOKUP(B151,[1]colour_range_groups!$B$2:$F$140,5,FALSE)</f>
         <v>C11</v>
       </c>
-      <c r="G151" t="s">
-        <v>67</v>
-      </c>
-      <c r="H151">
+      <c r="G151" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H151" s="4">
         <v>42</v>
       </c>
-      <c r="I151">
+      <c r="I151" s="4">
         <v>42</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
+      <c r="A152" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B152" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="C152" t="s">
+      <c r="C152" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D152">
+      <c r="D152" s="4">
         <v>27560</v>
       </c>
-      <c r="E152" t="s">
-        <v>279</v>
-      </c>
-      <c r="F152" t="str">
+      <c r="E152" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="F152" s="4" t="str">
         <f>VLOOKUP(B152,[1]colour_range_groups!$B$2:$F$140,5,FALSE)</f>
         <v>C10</v>
       </c>
-      <c r="G152" t="s">
-        <v>67</v>
-      </c>
-      <c r="H152">
+      <c r="G152" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H152" s="4">
         <v>61</v>
       </c>
-      <c r="I152">
+      <c r="I152" s="4">
         <v>61</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
+      <c r="A153" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B153" t="s">
+      <c r="B153" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="C153" t="s">
+      <c r="C153" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="D153" s="4">
+        <v>48909</v>
+      </c>
+      <c r="E153" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F153" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G153" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H153" s="4">
+        <v>61</v>
+      </c>
+      <c r="I153" s="4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A154" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C154" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D154" s="4">
+        <v>9865</v>
+      </c>
+      <c r="E154" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F154" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G154" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H154" s="4">
+        <v>61</v>
+      </c>
+      <c r="I154" s="4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A155" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C155" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="D155" s="4">
+        <v>19113</v>
+      </c>
+      <c r="E155" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F155" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G155" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H155" s="4">
+        <v>50</v>
+      </c>
+      <c r="I155" s="4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A156" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C156" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D156" s="4">
+        <v>3042</v>
+      </c>
+      <c r="E156" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F156" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G156" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H156" s="4">
+        <v>50</v>
+      </c>
+      <c r="I156" s="4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A157" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="C157" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D157" s="4">
+        <v>32268</v>
+      </c>
+      <c r="E157" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F157" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G157" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H157" s="4">
+        <v>50</v>
+      </c>
+      <c r="I157" s="4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A158" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C158" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="D158" s="4">
+        <v>13053</v>
+      </c>
+      <c r="E158" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F158" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G158" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H158" s="4">
+        <v>2357</v>
+      </c>
+      <c r="I158" s="4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A159" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="D159" s="4">
+        <v>19120</v>
+      </c>
+      <c r="E159" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F159" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G159" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H159" s="4">
+        <v>2357</v>
+      </c>
+      <c r="I159" s="4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A160" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D160" s="4">
+        <v>10499</v>
+      </c>
+      <c r="E160" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F160" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G160" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H160" s="4">
+        <v>2357</v>
+      </c>
+      <c r="I160" s="4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A161" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C161" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D161" s="4">
+        <v>27303</v>
+      </c>
+      <c r="E161" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F161" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G161" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H161" s="4">
+        <v>2357</v>
+      </c>
+      <c r="I161" s="4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A162" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C162" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="D162" s="4">
+        <v>12021</v>
+      </c>
+      <c r="E162" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F162" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G162" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H162" s="4">
+        <v>2357</v>
+      </c>
+      <c r="I162" s="4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A163" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C163" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="D163" s="4">
+        <v>1317</v>
+      </c>
+      <c r="E163" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F163" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G163" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H163" s="4">
+        <v>2357</v>
+      </c>
+      <c r="I163" s="4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A164" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C164" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="D153">
-        <v>48909</v>
-      </c>
-      <c r="E153" t="s">
-        <v>85</v>
-      </c>
-      <c r="F153" t="s">
-        <v>85</v>
-      </c>
-      <c r="G153" t="s">
-        <v>67</v>
-      </c>
-      <c r="H153">
+      <c r="D164" s="4">
+        <v>10644</v>
+      </c>
+      <c r="E164" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F164" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G164" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H164" s="4">
+        <v>2357</v>
+      </c>
+      <c r="I164" s="4">
         <v>61</v>
       </c>
-      <c r="I153">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
-        <v>55</v>
-      </c>
-      <c r="B154" t="s">
-        <v>189</v>
-      </c>
-      <c r="C154" t="s">
-        <v>5</v>
-      </c>
-      <c r="D154">
-        <v>9865</v>
-      </c>
-      <c r="E154" t="s">
-        <v>85</v>
-      </c>
-      <c r="F154" t="s">
-        <v>85</v>
-      </c>
-      <c r="G154" t="s">
-        <v>67</v>
-      </c>
-      <c r="H154">
-        <v>61</v>
-      </c>
-      <c r="I154">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
-        <v>56</v>
-      </c>
-      <c r="B155" t="s">
-        <v>190</v>
-      </c>
-      <c r="C155" t="s">
-        <v>283</v>
-      </c>
-      <c r="D155">
-        <v>19113</v>
-      </c>
-      <c r="E155" t="s">
-        <v>85</v>
-      </c>
-      <c r="F155" t="s">
-        <v>85</v>
-      </c>
-      <c r="G155" t="s">
-        <v>67</v>
-      </c>
-      <c r="H155">
-        <v>50</v>
-      </c>
-      <c r="I155">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
-        <v>56</v>
-      </c>
-      <c r="B156" t="s">
-        <v>191</v>
-      </c>
-      <c r="C156" t="s">
-        <v>5</v>
-      </c>
-      <c r="D156">
-        <v>3042</v>
-      </c>
-      <c r="E156" t="s">
-        <v>85</v>
-      </c>
-      <c r="F156" t="s">
-        <v>85</v>
-      </c>
-      <c r="G156" t="s">
-        <v>67</v>
-      </c>
-      <c r="H156">
-        <v>50</v>
-      </c>
-      <c r="I156">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
-        <v>56</v>
-      </c>
-      <c r="B157" t="s">
-        <v>192</v>
-      </c>
-      <c r="C157" t="s">
-        <v>13</v>
-      </c>
-      <c r="D157">
-        <v>32268</v>
-      </c>
-      <c r="E157" t="s">
-        <v>85</v>
-      </c>
-      <c r="F157" t="s">
-        <v>85</v>
-      </c>
-      <c r="G157" t="s">
-        <v>67</v>
-      </c>
-      <c r="H157">
-        <v>50</v>
-      </c>
-      <c r="I157">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
-        <v>57</v>
-      </c>
-      <c r="B158" t="s">
-        <v>193</v>
-      </c>
-      <c r="C158" t="s">
-        <v>284</v>
-      </c>
-      <c r="D158">
-        <v>13053</v>
-      </c>
-      <c r="E158" t="s">
-        <v>85</v>
-      </c>
-      <c r="F158" t="s">
-        <v>85</v>
-      </c>
-      <c r="G158" t="s">
-        <v>67</v>
-      </c>
-      <c r="H158">
-        <v>2357</v>
-      </c>
-      <c r="I158">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
-        <v>57</v>
-      </c>
-      <c r="B159" t="s">
-        <v>194</v>
-      </c>
-      <c r="C159" t="s">
-        <v>283</v>
-      </c>
-      <c r="D159">
-        <v>19120</v>
-      </c>
-      <c r="E159" t="s">
-        <v>85</v>
-      </c>
-      <c r="F159" t="s">
-        <v>85</v>
-      </c>
-      <c r="G159" t="s">
-        <v>67</v>
-      </c>
-      <c r="H159">
-        <v>2357</v>
-      </c>
-      <c r="I159">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
-        <v>57</v>
-      </c>
-      <c r="B160" t="s">
-        <v>195</v>
-      </c>
-      <c r="C160" t="s">
-        <v>5</v>
-      </c>
-      <c r="D160">
-        <v>10499</v>
-      </c>
-      <c r="E160" t="s">
-        <v>85</v>
-      </c>
-      <c r="F160" t="s">
-        <v>85</v>
-      </c>
-      <c r="G160" t="s">
-        <v>67</v>
-      </c>
-      <c r="H160">
-        <v>2357</v>
-      </c>
-      <c r="I160">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
-        <v>57</v>
-      </c>
-      <c r="B161" t="s">
-        <v>196</v>
-      </c>
-      <c r="C161" t="s">
-        <v>13</v>
-      </c>
-      <c r="D161">
-        <v>27303</v>
-      </c>
-      <c r="E161" t="s">
-        <v>85</v>
-      </c>
-      <c r="F161" t="s">
-        <v>85</v>
-      </c>
-      <c r="G161" t="s">
-        <v>67</v>
-      </c>
-      <c r="H161">
-        <v>2357</v>
-      </c>
-      <c r="I161">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
-        <v>57</v>
-      </c>
-      <c r="B162" t="s">
-        <v>197</v>
-      </c>
-      <c r="C162" t="s">
-        <v>298</v>
-      </c>
-      <c r="D162">
-        <v>12021</v>
-      </c>
-      <c r="E162" t="s">
-        <v>85</v>
-      </c>
-      <c r="F162" t="s">
-        <v>85</v>
-      </c>
-      <c r="G162" t="s">
-        <v>67</v>
-      </c>
-      <c r="H162">
-        <v>2357</v>
-      </c>
-      <c r="I162">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
-        <v>57</v>
-      </c>
-      <c r="B163" t="s">
-        <v>198</v>
-      </c>
-      <c r="C163" t="s">
-        <v>302</v>
-      </c>
-      <c r="D163">
-        <v>1317</v>
-      </c>
-      <c r="E163" t="s">
-        <v>85</v>
-      </c>
-      <c r="F163" t="s">
-        <v>85</v>
-      </c>
-      <c r="G163" t="s">
-        <v>67</v>
-      </c>
-      <c r="H163">
-        <v>2357</v>
-      </c>
-      <c r="I163">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
-        <v>57</v>
-      </c>
-      <c r="B164" t="s">
-        <v>199</v>
-      </c>
-      <c r="C164" t="s">
-        <v>292</v>
-      </c>
-      <c r="D164">
-        <v>10644</v>
-      </c>
-      <c r="E164" t="s">
-        <v>85</v>
-      </c>
-      <c r="F164" t="s">
-        <v>85</v>
-      </c>
-      <c r="G164" t="s">
-        <v>67</v>
-      </c>
-      <c r="H164">
-        <v>2357</v>
-      </c>
-      <c r="I164">
-        <v>61</v>
-      </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
+      <c r="A165" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B165" t="s">
+      <c r="B165" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="C165" t="s">
+      <c r="C165" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D165">
+      <c r="D165" s="4">
         <v>2718</v>
       </c>
-      <c r="E165" t="s">
-        <v>279</v>
-      </c>
-      <c r="F165" t="str">
+      <c r="E165" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="F165" s="4" t="str">
         <f>VLOOKUP(B165,[1]colour_range_groups!$B$2:$F$140,5,FALSE)</f>
         <v>C03</v>
       </c>
-      <c r="G165" t="s">
+      <c r="G165" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H165">
+      <c r="H165" s="4">
         <v>1096</v>
       </c>
-      <c r="I165">
+      <c r="I165" s="4">
         <v>828</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
+      <c r="A166" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B166" t="s">
+      <c r="B166" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="C166" t="s">
-        <v>297</v>
-      </c>
-      <c r="D166">
+      <c r="C166" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="D166" s="4">
         <v>20202</v>
       </c>
-      <c r="E166" t="s">
-        <v>85</v>
-      </c>
-      <c r="F166" t="s">
-        <v>85</v>
-      </c>
-      <c r="G166" t="s">
-        <v>67</v>
-      </c>
-      <c r="H166">
+      <c r="E166" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F166" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G166" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H166" s="4">
         <v>45</v>
       </c>
-      <c r="I166">
+      <c r="I166" s="4">
         <v>45</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
+      <c r="A167" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B167" t="s">
+      <c r="B167" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="C167" t="s">
-        <v>289</v>
-      </c>
-      <c r="D167">
+      <c r="C167" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="D167" s="4">
         <v>19773</v>
       </c>
-      <c r="E167" t="s">
-        <v>85</v>
-      </c>
-      <c r="F167" t="s">
-        <v>85</v>
-      </c>
-      <c r="G167" t="s">
-        <v>67</v>
-      </c>
-      <c r="H167">
+      <c r="E167" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F167" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G167" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H167" s="4">
         <v>45</v>
       </c>
-      <c r="I167">
+      <c r="I167" s="4">
         <v>45</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
+      <c r="A168" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B168" t="s">
+      <c r="B168" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C168" t="s">
+      <c r="C168" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D168">
+      <c r="D168" s="4">
         <v>34721</v>
       </c>
-      <c r="E168" t="s">
-        <v>85</v>
-      </c>
-      <c r="F168" t="s">
-        <v>85</v>
-      </c>
-      <c r="G168" t="s">
+      <c r="E168" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F168" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G168" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H168">
+      <c r="H168" s="4">
         <v>2256</v>
       </c>
-      <c r="I168">
+      <c r="I168" s="4">
         <v>828</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
+      <c r="A169" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B169" t="s">
+      <c r="B169" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="C169" t="s">
+      <c r="C169" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D169">
+      <c r="D169" s="4">
         <v>23542</v>
       </c>
-      <c r="E169" t="s">
-        <v>85</v>
-      </c>
-      <c r="F169" t="s">
-        <v>85</v>
-      </c>
-      <c r="G169" t="s">
+      <c r="E169" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F169" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G169" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H169">
+      <c r="H169" s="4">
         <v>2256</v>
       </c>
-      <c r="I169">
+      <c r="I169" s="4">
         <v>828</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
+      <c r="A170" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B170" t="s">
+      <c r="B170" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="C170" t="s">
-        <v>284</v>
-      </c>
-      <c r="D170">
+      <c r="C170" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="D170" s="4">
         <v>6348</v>
       </c>
-      <c r="E170" t="s">
-        <v>85</v>
-      </c>
-      <c r="F170" t="s">
-        <v>85</v>
-      </c>
-      <c r="G170" t="s">
+      <c r="E170" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F170" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G170" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H170">
+      <c r="H170" s="4">
         <v>2256</v>
       </c>
-      <c r="I170">
+      <c r="I170" s="4">
         <v>828</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
+      <c r="A171" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B171" t="s">
+      <c r="B171" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="C171" t="s">
+      <c r="C171" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D171">
+      <c r="D171" s="4">
         <v>22399</v>
       </c>
-      <c r="E171" t="s">
-        <v>85</v>
-      </c>
-      <c r="F171" t="s">
-        <v>85</v>
-      </c>
-      <c r="G171" t="s">
+      <c r="E171" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F171" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G171" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H171">
+      <c r="H171" s="4">
         <v>2256</v>
       </c>
-      <c r="I171">
+      <c r="I171" s="4">
         <v>828</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
+      <c r="A172" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B172" t="s">
+      <c r="B172" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="C172" t="s">
-        <v>282</v>
-      </c>
-      <c r="D172">
+      <c r="C172" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="D172" s="4">
         <v>22102</v>
       </c>
-      <c r="E172" t="s">
-        <v>85</v>
-      </c>
-      <c r="F172" t="s">
-        <v>85</v>
-      </c>
-      <c r="G172" t="s">
+      <c r="E172" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F172" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G172" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H172">
+      <c r="H172" s="4">
         <v>2256</v>
       </c>
-      <c r="I172">
+      <c r="I172" s="4">
         <v>828</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
+      <c r="A173" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B173" t="s">
+      <c r="B173" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="C173" t="s">
+      <c r="C173" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D173">
+      <c r="D173" s="4">
         <v>3327</v>
       </c>
-      <c r="E173" t="s">
-        <v>85</v>
-      </c>
-      <c r="F173" t="s">
-        <v>85</v>
-      </c>
-      <c r="G173" t="s">
+      <c r="E173" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F173" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G173" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H173">
+      <c r="H173" s="4">
         <v>2256</v>
       </c>
-      <c r="I173">
+      <c r="I173" s="4">
         <v>828</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
+      <c r="A174" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B174" t="s">
+      <c r="B174" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="C174" t="s">
-        <v>296</v>
-      </c>
-      <c r="D174">
+      <c r="C174" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="D174" s="4">
         <v>18616</v>
       </c>
-      <c r="E174" t="s">
-        <v>85</v>
-      </c>
-      <c r="F174" t="s">
-        <v>85</v>
-      </c>
-      <c r="G174" t="s">
+      <c r="E174" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F174" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G174" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H174">
+      <c r="H174" s="4">
         <v>3230</v>
       </c>
-      <c r="I174">
+      <c r="I174" s="4">
         <v>828</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
+      <c r="A175" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B175" t="s">
+      <c r="B175" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="C175" t="s">
+      <c r="C175" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D175">
+      <c r="D175" s="4">
         <v>25647</v>
       </c>
-      <c r="E175" t="s">
-        <v>279</v>
-      </c>
-      <c r="F175" t="str">
+      <c r="E175" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="F175" s="4" t="str">
         <f>VLOOKUP(B175,[1]colour_range_groups!$B$2:$F$140,5,FALSE)</f>
         <v>C13</v>
       </c>
-      <c r="G175" t="s">
+      <c r="G175" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H175">
+      <c r="H175" s="4">
         <v>3230</v>
       </c>
-      <c r="I175">
+      <c r="I175" s="4">
         <v>828</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
+      <c r="A176" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B176" t="s">
+      <c r="B176" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="C176" t="s">
+      <c r="C176" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="D176">
+      <c r="D176" s="4">
         <v>11999</v>
       </c>
-      <c r="E176" t="s">
-        <v>85</v>
-      </c>
-      <c r="F176" t="s">
-        <v>85</v>
-      </c>
-      <c r="G176" t="s">
+      <c r="E176" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F176" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G176" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H176">
+      <c r="H176" s="4">
         <v>3230</v>
       </c>
-      <c r="I176">
+      <c r="I176" s="4">
         <v>828</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A177" t="s">
+      <c r="A177" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B177" t="s">
+      <c r="B177" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="C177" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D177" s="5">
+        <v>39254</v>
+      </c>
+      <c r="E177" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="F177" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="C177" t="s">
-        <v>215</v>
-      </c>
-      <c r="D177" s="4">
-        <v>39254</v>
-      </c>
-      <c r="E177" t="s">
-        <v>279</v>
-      </c>
-      <c r="F177" t="s">
-        <v>273</v>
-      </c>
-      <c r="G177" t="s">
+      <c r="G177" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H177">
+      <c r="H177" s="4">
         <v>3230</v>
       </c>
-      <c r="I177">
+      <c r="I177" s="4">
         <v>828</v>
       </c>
     </row>
@@ -8998,7 +8998,7 @@
         <v>3222</v>
       </c>
       <c r="D3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E3" t="s">
         <v>82</v>
@@ -9015,7 +9015,7 @@
         <v>1115</v>
       </c>
       <c r="D4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E4" t="s">
         <v>82</v>
@@ -9079,11 +9079,11 @@
       <c r="B8" t="s">
         <v>65</v>
       </c>
-      <c r="C8" t="s">
-        <v>268</v>
-      </c>
-      <c r="D8" t="s">
-        <v>269</v>
+      <c r="C8">
+        <v>14595</v>
+      </c>
+      <c r="D8">
+        <v>828</v>
       </c>
       <c r="E8" t="s">
         <v>81</v>
@@ -9100,7 +9100,7 @@
         <v>900</v>
       </c>
       <c r="D9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E9" t="s">
         <v>83</v>
@@ -9134,7 +9134,7 @@
         <v>900</v>
       </c>
       <c r="D11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E11" t="s">
         <v>83</v>
@@ -9283,11 +9283,11 @@
       <c r="B20" t="s">
         <v>67</v>
       </c>
-      <c r="C20" t="s">
-        <v>268</v>
-      </c>
-      <c r="D20" t="s">
-        <v>269</v>
+      <c r="C20">
+        <v>12749</v>
+      </c>
+      <c r="D20">
+        <v>353</v>
       </c>
       <c r="E20" t="s">
         <v>81</v>
@@ -9372,7 +9372,7 @@
         <v>704</v>
       </c>
       <c r="D25" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E25" t="s">
         <v>84</v>
@@ -9389,7 +9389,7 @@
         <v>1030</v>
       </c>
       <c r="D26" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E26" t="s">
         <v>84</v>
@@ -9491,7 +9491,7 @@
         <v>3538</v>
       </c>
       <c r="D32" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E32" t="s">
         <v>81</v>
@@ -9708,11 +9708,11 @@
       <c r="B45" t="s">
         <v>67</v>
       </c>
-      <c r="C45" t="s">
-        <v>268</v>
-      </c>
-      <c r="D45" t="s">
-        <v>269</v>
+      <c r="C45">
+        <v>12762</v>
+      </c>
+      <c r="D45">
+        <v>61</v>
       </c>
       <c r="E45" t="s">
         <v>81</v>
@@ -9793,11 +9793,11 @@
       <c r="B50" t="s">
         <v>67</v>
       </c>
-      <c r="C50" t="s">
-        <v>268</v>
-      </c>
-      <c r="D50" t="s">
-        <v>269</v>
+      <c r="C50">
+        <v>14186</v>
+      </c>
+      <c r="D50">
+        <v>52</v>
       </c>
       <c r="E50" t="s">
         <v>84</v>
@@ -10067,6 +10067,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010001299E3986B667479987137D8ABC56EE" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="38a09d5c9a247073cfa35e79f6411387">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c478fcf1-df2b-4b17-ac0d-5fb1dd3b8dd4" xmlns:ns3="2a1e774b-1312-493c-b167-5aa786dea5b7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e5314cc11d213a1efe15b1656a8889f2" ns2:_="" ns3:_="">
     <xsd:import namespace="c478fcf1-df2b-4b17-ac0d-5fb1dd3b8dd4"/>
@@ -10277,15 +10286,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -10297,13 +10297,28 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75A4DFB8-8BD4-41E9-AB77-DEE4F2E130FC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C5C3192-5BBF-40E3-B3F1-BAC18B55C303}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C5C3192-5BBF-40E3-B3F1-BAC18B55C303}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75A4DFB8-8BD4-41E9-AB77-DEE4F2E130FC}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c478fcf1-df2b-4b17-ac0d-5fb1dd3b8dd4"/>
+    <ds:schemaRef ds:uri="2a1e774b-1312-493c-b167-5aa786dea5b7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
